--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{AF403817-6DD5-4072-845D-B46C3FFD0AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{163CBAB7-FF86-403E-BE21-3DF4A805C97F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4D1583-660A-4815-8FDE-C2567EA3B323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" activeTab="1" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
     <sheet name="01-10" sheetId="2" r:id="rId2"/>
     <sheet name="04-10" sheetId="3" r:id="rId3"/>
+    <sheet name="05-10" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="62">
   <si>
     <t>Date</t>
   </si>
@@ -186,6 +187,48 @@
   </si>
   <si>
     <t>0171ICS0015</t>
+  </si>
+  <si>
+    <t>CAAU640372 /2</t>
+  </si>
+  <si>
+    <t>FFAU501814 /0</t>
+  </si>
+  <si>
+    <t>00380-506-31</t>
+  </si>
+  <si>
+    <t>00217-507-31</t>
+  </si>
+  <si>
+    <t>ARKU150130 /6</t>
+  </si>
+  <si>
+    <t>1441385</t>
+  </si>
+  <si>
+    <t>00141-525-31</t>
+  </si>
+  <si>
+    <t>HASU492916 /6</t>
+  </si>
+  <si>
+    <t>HASU5156746 /8</t>
+  </si>
+  <si>
+    <t>MRSU698006 /4</t>
+  </si>
+  <si>
+    <t>CAIU634538 /3</t>
+  </si>
+  <si>
+    <t>J1803692</t>
+  </si>
+  <si>
+    <t>00582-510-31</t>
+  </si>
+  <si>
+    <t>001766-508-31</t>
   </si>
 </sst>
 </file>
@@ -292,7 +335,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -344,12 +387,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -578,26 +615,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -726,8 +760,59 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>933450</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152397</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2888A717-941B-42BF-A098-CE87885688D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="180975" y="0"/>
+          <a:ext cx="2000250" cy="533397"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1129,16 +1214,16 @@
         <v>46299</v>
       </c>
       <c r="B3" s="3">
-        <f>'04-10'!H1</f>
-        <v>0</v>
+        <f>'04-10'!J1</f>
+        <v>5</v>
       </c>
       <c r="C3" s="3">
-        <f>'04-10'!H2</f>
-        <v>0</v>
+        <f>'04-10'!J2</f>
+        <v>3</v>
       </c>
       <c r="D3" s="4">
         <f>B3+C3</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3" s="3"/>
     </row>
@@ -1296,15 +1381,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D19)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1363,16 +1448,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -1762,7 +1847,7 @@
       <c r="B36" s="19">
         <v>1102026</v>
       </c>
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="51" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="33"/>
@@ -1780,7 +1865,7 @@
       <c r="B37" s="19">
         <v>1102026</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="52" t="s">
         <v>26</v>
       </c>
       <c r="D37" s="33"/>
@@ -1867,8 +1952,9 @@
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1889,6 +1975,589 @@
     <col min="12" max="16384" width="11.42578125" style="23"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="J1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>5</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="H2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="8">
+        <f>COUNTA(C20:C29)-H2</f>
+        <v>3</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+    </row>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="19">
+        <v>4102026</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="22"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="19">
+        <v>4102026</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="22"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="19">
+        <v>4102026</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="22"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="19">
+        <v>4102026</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="22"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="19">
+        <v>4102026</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="22"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="47"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="22"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="22"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="22"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="30">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>4102026</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="33">
+        <v>3666</v>
+      </c>
+      <c r="F20" s="33">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="30">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19">
+        <v>4102026</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="50">
+        <v>3669</v>
+      </c>
+      <c r="F21" s="33">
+        <v>40</v>
+      </c>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="30">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19">
+        <v>4102026</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="26">
+        <v>20</v>
+      </c>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="30">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="31"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="31"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="30">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="31"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="31"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="30">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="31"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="30">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="31"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="30">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="30"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="30">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="30"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="39"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="39"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="30">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="30">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="30">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="30">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="30">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="33">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="33">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="30"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{2C47AF88-9A31-4D84-B329-10A92F3AA1C7}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15 F21:F22" xr:uid="{06CE73C6-C0D9-4337-9429-05602BB111C3}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E68CDFBC-7B67-49C8-BC1D-EC76810F57FF}">
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="23" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="23" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="23"/>
+    <col min="11" max="11" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="23"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="H1" s="8">
@@ -1910,7 +2579,7 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C20:C29)-F2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
@@ -1921,16 +2590,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -1941,7 +2610,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="12">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1972,101 +2641,62 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>35</v>
-      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="26"/>
       <c r="G8" s="22"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="53" t="s">
-        <v>46</v>
-      </c>
+      <c r="B9" s="48"/>
       <c r="C9" s="19"/>
-      <c r="D9" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>38</v>
-      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="53" t="s">
-        <v>46</v>
-      </c>
+      <c r="B10" s="48"/>
       <c r="C10" s="19"/>
-      <c r="D10" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>38</v>
-      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="53" t="s">
-        <v>47</v>
-      </c>
+      <c r="B11" s="48"/>
       <c r="C11" s="19"/>
-      <c r="D11" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>35</v>
-      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
       <c r="G11" s="22"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="53" t="s">
-        <v>47</v>
-      </c>
+      <c r="B12" s="48"/>
       <c r="C12" s="19"/>
-      <c r="D12" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>35</v>
-      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="26"/>
       <c r="G12" s="22"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="52"/>
+      <c r="B13" s="47"/>
       <c r="C13" s="19"/>
       <c r="D13" s="26"/>
       <c r="E13" s="27"/>
@@ -2142,21 +2772,41 @@
       <c r="A20" s="30">
         <v>1</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
+      <c r="B20" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="43">
+        <v>3617</v>
+      </c>
+      <c r="F20" s="33">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="30">
         <v>2</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="30"/>
+      <c r="B21" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="43">
+        <v>3618</v>
+      </c>
+      <c r="F21" s="33">
+        <v>40</v>
+      </c>
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
       <c r="K21" s="35"/>
@@ -2327,63 +2977,93 @@
         <v>1</v>
       </c>
       <c r="B35" s="19">
-        <v>4102026</v>
-      </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
+        <v>5102026</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="33">
+        <v>3715</v>
+      </c>
+      <c r="E35" s="43">
+        <v>3621</v>
+      </c>
+      <c r="F35" s="43">
+        <v>40</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="30">
         <v>2</v>
       </c>
       <c r="B36" s="19">
-        <v>1102026</v>
-      </c>
-      <c r="C36" s="50"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
+        <v>5102026</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="33">
+        <v>3713</v>
+      </c>
+      <c r="E36" s="43">
+        <v>3622</v>
+      </c>
+      <c r="F36" s="43">
+        <v>40</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="30">
         <v>3</v>
       </c>
       <c r="B37" s="19">
-        <v>1102026</v>
-      </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
+        <v>5102026</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="33">
+        <v>3716</v>
+      </c>
+      <c r="E37" s="43">
+        <v>3623</v>
+      </c>
+      <c r="F37" s="43">
+        <v>40</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>4</v>
       </c>
       <c r="B38" s="19">
-        <v>1102026</v>
-      </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
+        <v>5102026</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="33">
+        <v>3620</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>5</v>
       </c>
-      <c r="B39" s="19">
-        <v>1102026</v>
-      </c>
+      <c r="B39" s="19"/>
       <c r="C39" s="36"/>
       <c r="D39" s="36"/>
       <c r="E39" s="43"/>
       <c r="F39" s="43"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="44">
+      <c r="A40" s="33">
         <v>6</v>
       </c>
       <c r="B40" s="19"/>
@@ -2393,7 +3073,7 @@
       <c r="F40" s="33"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="44">
+      <c r="A41" s="33">
         <v>7</v>
       </c>
       <c r="B41" s="19"/>
@@ -2410,12 +3090,12 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{2C47AF88-9A31-4D84-B329-10A92F3AA1C7}">
-      <formula1>"20,40,45,50"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15" xr:uid="{06CE73C6-C0D9-4337-9429-05602BB111C3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15 F21 F38" xr:uid="{B1D50973-C163-457B-B6A0-81FD3FC3B9BA}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{D73474D1-92DB-478B-93C4-9DC05452680F}">
+      <formula1>"20,40,45,50"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4D1583-660A-4815-8FDE-C2567EA3B323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{4B4D1583-660A-4815-8FDE-C2567EA3B323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C7E578-1FED-44D4-9545-51D4CE70F04A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" activeTab="1" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -479,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -621,17 +621,11 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1231,9 +1225,18 @@
       <c r="A4" s="2">
         <v>46300</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
+      <c r="B4" s="3">
+        <f>'05-10'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <f>'05-10'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D4" s="4">
+        <f>B4+C4</f>
+        <v>2</v>
+      </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -1385,11 +1388,11 @@
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D19)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1448,16 +1451,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -1847,7 +1850,7 @@
       <c r="B36" s="19">
         <v>1102026</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="33"/>
@@ -1865,7 +1868,7 @@
       <c r="B37" s="19">
         <v>1102026</v>
       </c>
-      <c r="C37" s="52" t="s">
+      <c r="C37" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D37" s="33"/>
@@ -2007,16 +2010,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2268,7 +2271,7 @@
       <c r="D21" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="49">
         <v>3669</v>
       </c>
       <c r="F21" s="33">
@@ -2590,16 +2593,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>

--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0AB0B5A2ED962CAE/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{4B4D1583-660A-4815-8FDE-C2567EA3B323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C7E578-1FED-44D4-9545-51D4CE70F04A}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{268A7E5D-2F6F-4219-A3FF-0CDC0150617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2593E2E1-1BEC-4034-9416-68274F1A0A0A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
@@ -17,8 +17,11 @@
     <sheet name="01-10" sheetId="2" r:id="rId2"/>
     <sheet name="04-10" sheetId="3" r:id="rId3"/>
     <sheet name="05-10" sheetId="4" r:id="rId4"/>
+    <sheet name="06-10" sheetId="5" r:id="rId5"/>
+    <sheet name="07-10" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="144">
   <si>
     <t>Date</t>
   </si>
@@ -229,6 +232,252 @@
   </si>
   <si>
     <t>001766-508-31</t>
+  </si>
+  <si>
+    <t>ECMU614116 /8</t>
+  </si>
+  <si>
+    <t>06230-586-48</t>
+  </si>
+  <si>
+    <t>HDMU321504 /6</t>
+  </si>
+  <si>
+    <t>25H1013125</t>
+  </si>
+  <si>
+    <t>HDMU341436 /7</t>
+  </si>
+  <si>
+    <t>25H1041732</t>
+  </si>
+  <si>
+    <t>HDMU342017 /0</t>
+  </si>
+  <si>
+    <t>25H1175272</t>
+  </si>
+  <si>
+    <t>HDMU342266 /0</t>
+  </si>
+  <si>
+    <t>25H1175275</t>
+  </si>
+  <si>
+    <t>KOCU430655 /1</t>
+  </si>
+  <si>
+    <t>26H0234922</t>
+  </si>
+  <si>
+    <t>TIIU600821 /4</t>
+  </si>
+  <si>
+    <t>26H0236033</t>
+  </si>
+  <si>
+    <t>00140-525-31</t>
+  </si>
+  <si>
+    <t>00362-516-31</t>
+  </si>
+  <si>
+    <t>00325-516-31</t>
+  </si>
+  <si>
+    <t>00125-523-31</t>
+  </si>
+  <si>
+    <t>00296-515-31</t>
+  </si>
+  <si>
+    <t>00139-525-31</t>
+  </si>
+  <si>
+    <t>TCNU857774 /0</t>
+  </si>
+  <si>
+    <t>CN6455438</t>
+  </si>
+  <si>
+    <t>CAAU692306 /7</t>
+  </si>
+  <si>
+    <t>CN6229789</t>
+  </si>
+  <si>
+    <t>LB0268981</t>
+  </si>
+  <si>
+    <t>YMLU329259 /5</t>
+  </si>
+  <si>
+    <t>LB0268982</t>
+  </si>
+  <si>
+    <t>TTNU375141 /0</t>
+  </si>
+  <si>
+    <t>LB0268826</t>
+  </si>
+  <si>
+    <t>TEMU349977 /4</t>
+  </si>
+  <si>
+    <t>LB0268825</t>
+  </si>
+  <si>
+    <t>TEMU346844 /9</t>
+  </si>
+  <si>
+    <t>LB0268771</t>
+  </si>
+  <si>
+    <t>TDTU171047 /5</t>
+  </si>
+  <si>
+    <t>LB0268871</t>
+  </si>
+  <si>
+    <t>TDRU255456 /0</t>
+  </si>
+  <si>
+    <t>LB0268773</t>
+  </si>
+  <si>
+    <t>SLDU283019 /1</t>
+  </si>
+  <si>
+    <t>LB0268987</t>
+  </si>
+  <si>
+    <t>PCIU306800 /4</t>
+  </si>
+  <si>
+    <t>LB0268829</t>
+  </si>
+  <si>
+    <t>OOLU288929 /7</t>
+  </si>
+  <si>
+    <t>LB0268828</t>
+  </si>
+  <si>
+    <t>OOLU161730 /8</t>
+  </si>
+  <si>
+    <t>LB0268983</t>
+  </si>
+  <si>
+    <t>MFCU260329 /9</t>
+  </si>
+  <si>
+    <t>LB0268776</t>
+  </si>
+  <si>
+    <t>MBSU281359 /8</t>
+  </si>
+  <si>
+    <t>LB0268821</t>
+  </si>
+  <si>
+    <t>MBSU281322 /1</t>
+  </si>
+  <si>
+    <t>LB0268775</t>
+  </si>
+  <si>
+    <t>MBSU281306 /8</t>
+  </si>
+  <si>
+    <t>LB0268872</t>
+  </si>
+  <si>
+    <t>MBSU281304 /7</t>
+  </si>
+  <si>
+    <t>LB0268988</t>
+  </si>
+  <si>
+    <t>MBSU281295 /0</t>
+  </si>
+  <si>
+    <t>LB0268823</t>
+  </si>
+  <si>
+    <t>MBSU281261 /0</t>
+  </si>
+  <si>
+    <t>LB0268989</t>
+  </si>
+  <si>
+    <t>MBSU281245 /7</t>
+  </si>
+  <si>
+    <t>LB0268824</t>
+  </si>
+  <si>
+    <t>MBSU281087 /6</t>
+  </si>
+  <si>
+    <t>LB0268990</t>
+  </si>
+  <si>
+    <t>MBSU280824 /6</t>
+  </si>
+  <si>
+    <t>LB0268985</t>
+  </si>
+  <si>
+    <t>MBSU280770 /1</t>
+  </si>
+  <si>
+    <t>LB0268986</t>
+  </si>
+  <si>
+    <t>MBSU280656 /2</t>
+  </si>
+  <si>
+    <t>LB0268827</t>
+  </si>
+  <si>
+    <t>MBSU280648 /0</t>
+  </si>
+  <si>
+    <t>LB0268822</t>
+  </si>
+  <si>
+    <t>KKTU710450 /3</t>
+  </si>
+  <si>
+    <t>0040ICS0002</t>
+  </si>
+  <si>
+    <t>25H1489025</t>
+  </si>
+  <si>
+    <t>25H1489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0764ICS0062 </t>
+  </si>
+  <si>
+    <t>HMMU424163 /9</t>
+  </si>
+  <si>
+    <t>HMMU498102 /3</t>
+  </si>
+  <si>
+    <t>MRSU215858 /4</t>
+  </si>
+  <si>
+    <t>CN8343648</t>
+  </si>
+  <si>
+    <t>MSNU928137 /8</t>
+  </si>
+  <si>
+    <t>FX47338080</t>
   </si>
 </sst>
 </file>
@@ -239,7 +488,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,8 +583,22 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,8 +653,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -475,11 +744,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -536,12 +842,6 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -624,7 +924,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -797,6 +1145,116 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="180975" y="0"/>
+          <a:ext cx="2000250" cy="533397"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133347</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6656C31-123B-4246-BE51-3C02C2C4C123}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="533397"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152397</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E27370C-0E26-48E3-BE53-BCE14CC1DFD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
           <a:ext cx="2000250" cy="533397"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1231,11 +1689,11 @@
       </c>
       <c r="C4" s="3">
         <f>'05-10'!H2</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4" s="4">
         <f>B4+C4</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F4" s="3"/>
     </row>
@@ -1243,18 +1701,36 @@
       <c r="A5" s="2">
         <v>46301</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="3">
+        <f>'06-10'!H1</f>
+        <v>14</v>
+      </c>
+      <c r="C5" s="3">
+        <f>'06-10'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>14</v>
+      </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46302</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
+      <c r="B6" s="3">
+        <f>'07-10'!H1</f>
+        <v>12</v>
+      </c>
+      <c r="C6" s="3">
+        <f>'07-10'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <f>B6+C6</f>
+        <v>12</v>
+      </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -1384,15 +1860,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D19)</f>
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1407,16 +1883,16 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.42578125" style="23"/>
-    <col min="11" max="11" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="23"/>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1451,16 +1927,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -1504,95 +1980,95 @@
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="19"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="24"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="19"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="19"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="22"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="24"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="19"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="22"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="24"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="19"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="22"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="24"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="19"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="22"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="24"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="19"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="22"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="19"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="22"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="22"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -1630,162 +2106,162 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="A20" s="28">
         <v>1</v>
       </c>
       <c r="B20" s="19">
         <v>1102026</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="31">
         <v>3611</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="31">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30">
+      <c r="A21" s="28">
         <v>2</v>
       </c>
       <c r="B21" s="19"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="30"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="28"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+      <c r="A22" s="28">
         <v>3</v>
       </c>
       <c r="B22" s="19"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="31"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="29"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30">
+      <c r="A23" s="28">
         <v>4</v>
       </c>
       <c r="B23" s="19"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="31"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="29"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30">
+      <c r="A24" s="28">
         <v>5</v>
       </c>
       <c r="B24" s="19"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="31"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="29"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="30">
+      <c r="A25" s="28">
         <v>6</v>
       </c>
       <c r="B25" s="19"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="31"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="29"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30">
+      <c r="A26" s="28">
         <v>7</v>
       </c>
       <c r="B26" s="19"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="31"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="29"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="30">
+      <c r="A27" s="28">
         <v>8</v>
       </c>
       <c r="B27" s="19"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="31"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="29"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="30">
+      <c r="A28" s="28">
         <v>9</v>
       </c>
       <c r="B28" s="19"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="31"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="29"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="30">
+      <c r="A29" s="28">
         <v>10</v>
       </c>
       <c r="B29" s="19"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="30"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30">
+      <c r="A30" s="28">
         <v>11</v>
       </c>
       <c r="B30" s="19"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="30"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
       <c r="D31"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="37"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
@@ -1824,123 +2300,123 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="30">
+      <c r="A35" s="28">
         <v>1</v>
       </c>
       <c r="B35" s="19">
         <v>1102026</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="43">
+      <c r="E35" s="41">
         <v>3614</v>
       </c>
-      <c r="F35" s="43">
+      <c r="F35" s="41">
         <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="30">
+      <c r="A36" s="28">
         <v>2</v>
       </c>
       <c r="B36" s="19">
         <v>1102026</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="43">
+      <c r="D36" s="31"/>
+      <c r="E36" s="41">
         <v>3615</v>
       </c>
-      <c r="F36" s="43">
+      <c r="F36" s="41">
         <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="30">
+      <c r="A37" s="28">
         <v>3</v>
       </c>
       <c r="B37" s="19">
         <v>1102026</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="43">
+      <c r="D37" s="31"/>
+      <c r="E37" s="41">
         <v>3616</v>
       </c>
-      <c r="F37" s="43">
+      <c r="F37" s="41">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="30">
+      <c r="A38" s="28">
         <v>4</v>
       </c>
       <c r="B38" s="19">
         <v>1102026</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="C38" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E38" s="43">
+      <c r="E38" s="41">
         <v>3617</v>
       </c>
-      <c r="F38" s="43">
+      <c r="F38" s="41">
         <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="30">
+      <c r="A39" s="28">
         <v>5</v>
       </c>
       <c r="B39" s="19">
         <v>1102026</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="41">
         <v>3618</v>
       </c>
-      <c r="F39" s="43">
+      <c r="F39" s="41">
         <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="44">
+      <c r="A40" s="42">
         <v>6</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="44">
+      <c r="A41" s="42">
         <v>7</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="28"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F42" s="46"/>
+      <c r="F42" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1966,16 +2442,16 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.42578125" style="23"/>
-    <col min="11" max="11" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="23"/>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -2010,16 +2486,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2061,147 +2537,147 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="28" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="19">
         <v>4102026</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="22"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="46" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="19">
         <v>4102026</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="46" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="19">
         <v>4102026</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="22"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="46" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="19">
         <v>4102026</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="22"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="46" t="s">
         <v>47</v>
       </c>
       <c r="C12" s="19">
         <v>4102026</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="47"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="19"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="22"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="24"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="19"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="22"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="19"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="22"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="22"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -2239,182 +2715,182 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="A20" s="28">
         <v>1</v>
       </c>
       <c r="B20" s="19">
         <v>4102026</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="31">
         <v>3666</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="31">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30">
+      <c r="A21" s="28">
         <v>2</v>
       </c>
       <c r="B21" s="19">
         <v>4102026</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="47">
         <v>3669</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="31">
         <v>40</v>
       </c>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+      <c r="A22" s="28">
         <v>3</v>
       </c>
       <c r="B22" s="19">
         <v>4102026</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="24">
         <v>20</v>
       </c>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30">
+      <c r="A23" s="28">
         <v>4</v>
       </c>
       <c r="B23" s="19"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="31"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="29"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30">
+      <c r="A24" s="28">
         <v>5</v>
       </c>
       <c r="B24" s="19"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="31"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="29"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="30">
+      <c r="A25" s="28">
         <v>6</v>
       </c>
       <c r="B25" s="19"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="31"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="29"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30">
+      <c r="A26" s="28">
         <v>7</v>
       </c>
       <c r="B26" s="19"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="31"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="29"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="30">
+      <c r="A27" s="28">
         <v>8</v>
       </c>
       <c r="B27" s="19"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="31"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="29"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="30">
+      <c r="A28" s="28">
         <v>9</v>
       </c>
       <c r="B28" s="19"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="31"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="29"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="30">
+      <c r="A29" s="28">
         <v>10</v>
       </c>
       <c r="B29" s="19"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="30"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30">
+      <c r="A30" s="28">
         <v>11</v>
       </c>
       <c r="B30" s="19"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="30"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
       <c r="D31"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="37"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
@@ -2453,77 +2929,77 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="30">
+      <c r="A35" s="28">
         <v>1</v>
       </c>
       <c r="B35" s="19"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="30">
+      <c r="A36" s="28">
         <v>2</v>
       </c>
       <c r="B36" s="19"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="30">
+      <c r="A37" s="28">
         <v>3</v>
       </c>
       <c r="B37" s="19"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="30">
+      <c r="A38" s="28">
         <v>4</v>
       </c>
       <c r="B38" s="19"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="30">
+      <c r="A39" s="28">
         <v>5</v>
       </c>
       <c r="B39" s="19"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="33">
+      <c r="A40" s="31">
         <v>6</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="33">
+      <c r="A41" s="31">
         <v>7</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="28"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F42" s="46"/>
+      <c r="F42" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2549,16 +3025,16 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.42578125" style="23"/>
-    <col min="11" max="11" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="23"/>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -2582,7 +3058,7 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C20:C29)-F2</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
@@ -2593,16 +3069,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2644,97 +3120,97 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="30"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="19"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="48"/>
+      <c r="B9" s="46"/>
       <c r="C9" s="19"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="48"/>
+      <c r="B10" s="46"/>
       <c r="C10" s="19"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="22"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="48"/>
+      <c r="B11" s="46"/>
       <c r="C11" s="19"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="22"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="46"/>
       <c r="C12" s="19"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="22"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="47"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="19"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="22"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="24"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="19"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="22"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="19"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="22"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="22"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -2772,172 +3248,242 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="A20" s="28">
         <v>1</v>
       </c>
       <c r="B20" s="19">
         <v>5102026</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="41">
         <v>3617</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="31">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30">
+      <c r="A21" s="28">
         <v>2</v>
       </c>
       <c r="B21" s="19">
         <v>5102026</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="41">
         <v>3618</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="31">
         <v>40</v>
       </c>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+      <c r="A22" s="28">
         <v>3</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="31"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="B22" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="32">
+        <v>3614</v>
+      </c>
+      <c r="F22" s="29">
+        <v>45</v>
+      </c>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30">
+      <c r="A23" s="28">
         <v>4</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="31"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
+      <c r="B23" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30">
+      <c r="A24" s="28">
         <v>5</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="31"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
+      <c r="B24" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="30">
+      <c r="A25" s="28">
         <v>6</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="31"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
+      <c r="B25" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30">
+      <c r="A26" s="28">
         <v>7</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="31"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
+      <c r="B26" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="30">
+      <c r="A27" s="28">
         <v>8</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="31"/>
+      <c r="B27" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="24">
+        <v>40</v>
+      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="30">
+      <c r="A28" s="28">
         <v>9</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="31"/>
+      <c r="B28" s="19">
+        <v>5102026</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="24">
+        <v>40</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="30">
+      <c r="A29" s="28">
         <v>10</v>
       </c>
       <c r="B29" s="19"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="30"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30">
+      <c r="A30" s="28">
         <v>11</v>
       </c>
       <c r="B30" s="19"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="30"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
       <c r="D31"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="37"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
@@ -2976,124 +3522,124 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="30">
+      <c r="A35" s="28">
         <v>1</v>
       </c>
       <c r="B35" s="19">
         <v>5102026</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="31">
         <v>3715</v>
       </c>
-      <c r="E35" s="43">
+      <c r="E35" s="41">
         <v>3621</v>
       </c>
-      <c r="F35" s="43">
+      <c r="F35" s="41">
         <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="30">
+      <c r="A36" s="28">
         <v>2</v>
       </c>
       <c r="B36" s="19">
         <v>5102026</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="31">
         <v>3713</v>
       </c>
-      <c r="E36" s="43">
+      <c r="E36" s="41">
         <v>3622</v>
       </c>
-      <c r="F36" s="43">
+      <c r="F36" s="41">
         <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="30">
+      <c r="A37" s="28">
         <v>3</v>
       </c>
       <c r="B37" s="19">
         <v>5102026</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="33">
+      <c r="D37" s="31">
         <v>3716</v>
       </c>
-      <c r="E37" s="43">
+      <c r="E37" s="41">
         <v>3623</v>
       </c>
-      <c r="F37" s="43">
+      <c r="F37" s="41">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="30">
+      <c r="A38" s="28">
         <v>4</v>
       </c>
       <c r="B38" s="19">
         <v>5102026</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="31">
         <v>3620</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F38" s="24" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="30">
+      <c r="A39" s="28">
         <v>5</v>
       </c>
       <c r="B39" s="19"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="33">
+      <c r="A40" s="31">
         <v>6</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="33">
+      <c r="A41" s="31">
         <v>7</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="28"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F42" s="46"/>
+      <c r="F42" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15 F21 F38" xr:uid="{B1D50973-C163-457B-B6A0-81FD3FC3B9BA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15 F21 F38 F23:F28" xr:uid="{B1D50973-C163-457B-B6A0-81FD3FC3B9BA}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3101,7 +3647,1289 @@
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A16EF8D-37CA-4A31-8D52-A76DF0BB1357}">
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C31,"&lt;&gt;")</f>
+        <v>14</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B36:B37,"&lt;&gt;",C36:C37,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C36:C37)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E36:E37,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="59"/>
+      <c r="C9" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="59"/>
+      <c r="C11" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="59"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="59"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="59"/>
+      <c r="C15" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>9</v>
+      </c>
+      <c r="B16" s="59"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>10</v>
+      </c>
+      <c r="B17" s="59"/>
+      <c r="C17" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>11</v>
+      </c>
+      <c r="B18" s="59"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>12</v>
+      </c>
+      <c r="B19" s="59"/>
+      <c r="C19" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>13</v>
+      </c>
+      <c r="B20" s="59"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>14</v>
+      </c>
+      <c r="B21" s="59"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
+        <v>15</v>
+      </c>
+      <c r="B22" s="59"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
+        <v>16</v>
+      </c>
+      <c r="B23" s="59"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <v>17</v>
+      </c>
+      <c r="B24" s="59"/>
+      <c r="C24" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="20"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
+        <v>18</v>
+      </c>
+      <c r="B25" s="59"/>
+      <c r="C25" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D25" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="20"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
+        <v>19</v>
+      </c>
+      <c r="B26" s="59"/>
+      <c r="C26" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D26" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <v>20</v>
+      </c>
+      <c r="B27" s="59"/>
+      <c r="C27" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="20"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <v>21</v>
+      </c>
+      <c r="B28" s="59"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="20"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
+        <v>22</v>
+      </c>
+      <c r="B29" s="59"/>
+      <c r="C29" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
+        <v>23</v>
+      </c>
+      <c r="B30" s="59"/>
+      <c r="C30" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D30" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
+        <v>24</v>
+      </c>
+      <c r="B31" s="60"/>
+      <c r="C31" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="D31" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="28"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33"/>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="37"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="39"/>
+      <c r="D38"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="37"/>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+      <c r="B39" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="28">
+        <v>1</v>
+      </c>
+      <c r="B42" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" s="41">
+        <v>3619</v>
+      </c>
+      <c r="F42" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="28">
+        <v>2</v>
+      </c>
+      <c r="B43" s="19">
+        <v>6102026</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43" s="41">
+        <v>3624</v>
+      </c>
+      <c r="F43" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F44" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:B31"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F32" xr:uid="{F37D934B-5D51-4F04-83AC-DE8D0264A666}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A960496-9B69-4504-85DD-0BDC7520975C}">
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C20,"&lt;&gt;")</f>
+        <v>12</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B27:B31,"&lt;&gt;",C27:C31,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C27:C31)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E27:E31,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="63"/>
+      <c r="C9" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="63"/>
+      <c r="C10" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="63"/>
+      <c r="C11" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="63"/>
+      <c r="C15" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>10</v>
+      </c>
+      <c r="B17" s="63"/>
+      <c r="C17" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>11</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>12</v>
+      </c>
+      <c r="B19" s="63"/>
+      <c r="C19" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="28">
+        <v>13</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="61"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="61"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>1</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>2</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="28"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>3</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="29"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>4</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="29"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>5</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="29"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="37"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="31">
+        <v>3625</v>
+      </c>
+      <c r="F36" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19">
+        <v>7102026</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" s="31">
+        <v>3626</v>
+      </c>
+      <c r="F37" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F38" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:B17"/>
+    <mergeCell ref="B18:B19"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F23" xr:uid="{0C7EFAEC-AA73-4A53-AC68-E55C58105268}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0AB0B5A2ED962CAE/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{268A7E5D-2F6F-4219-A3FF-0CDC0150617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2593E2E1-1BEC-4034-9416-68274F1A0A0A}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{268A7E5D-2F6F-4219-A3FF-0CDC0150617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4669A96C-1B39-4554-A9F9-24A8525A00D0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" activeTab="7" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="05-10" sheetId="4" r:id="rId4"/>
     <sheet name="06-10" sheetId="5" r:id="rId5"/>
     <sheet name="07-10" sheetId="6" r:id="rId6"/>
+    <sheet name="08-10" sheetId="7" r:id="rId7"/>
+    <sheet name="11-10" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="202">
   <si>
     <t>Date</t>
   </si>
@@ -478,6 +479,180 @@
   </si>
   <si>
     <t>FX47338080</t>
+  </si>
+  <si>
+    <t>MSDU997113 /6</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>MSMU661001 /2</t>
+  </si>
+  <si>
+    <t>0674611</t>
+  </si>
+  <si>
+    <t>UETU703460 /0</t>
+  </si>
+  <si>
+    <t>0674567</t>
+  </si>
+  <si>
+    <t>00096-511-31</t>
+  </si>
+  <si>
+    <t>00463-509-31</t>
+  </si>
+  <si>
+    <t>00090-512-31</t>
+  </si>
+  <si>
+    <t>MEDU636673 /0</t>
+  </si>
+  <si>
+    <t>LG00690422</t>
+  </si>
+  <si>
+    <t>BMOU474366 /5</t>
+  </si>
+  <si>
+    <t>5878917</t>
+  </si>
+  <si>
+    <t>MEDU723902 /6</t>
+  </si>
+  <si>
+    <t>1128635</t>
+  </si>
+  <si>
+    <t>MEDU798835 /9</t>
+  </si>
+  <si>
+    <t>1128684</t>
+  </si>
+  <si>
+    <t>MSDU534494 /5</t>
+  </si>
+  <si>
+    <t>1146995</t>
+  </si>
+  <si>
+    <t>SEGU549541 /0</t>
+  </si>
+  <si>
+    <t>1128683</t>
+  </si>
+  <si>
+    <t>TGBU550533 /0</t>
+  </si>
+  <si>
+    <t>1128686</t>
+  </si>
+  <si>
+    <t>TRHU681016 /3</t>
+  </si>
+  <si>
+    <t>1146994</t>
+  </si>
+  <si>
+    <t>CAAU489835 /0</t>
+  </si>
+  <si>
+    <t>OM0092412</t>
+  </si>
+  <si>
+    <t>CAAU608029 /7</t>
+  </si>
+  <si>
+    <t>OM0092455</t>
+  </si>
+  <si>
+    <t>GCXU572967 /8</t>
+  </si>
+  <si>
+    <t>OM0092415</t>
+  </si>
+  <si>
+    <t>MRSU870794 /8</t>
+  </si>
+  <si>
+    <t>OM0092440</t>
+  </si>
+  <si>
+    <t>TCKU701928 /8</t>
+  </si>
+  <si>
+    <t>OM0092557</t>
+  </si>
+  <si>
+    <t>TCNU297401 /5</t>
+  </si>
+  <si>
+    <t>OM0092479</t>
+  </si>
+  <si>
+    <t>MRKU353739 /0</t>
+  </si>
+  <si>
+    <t>CN9008091</t>
+  </si>
+  <si>
+    <t>MRKU733342 /9</t>
+  </si>
+  <si>
+    <t>CN7978124</t>
+  </si>
+  <si>
+    <t>0178ICS0007</t>
+  </si>
+  <si>
+    <t>0178ICS0003</t>
+  </si>
+  <si>
+    <t>0178ICS0056</t>
+  </si>
+  <si>
+    <t>0106ICS0007</t>
+  </si>
+  <si>
+    <t>0106ICS0044</t>
+  </si>
+  <si>
+    <t>0106ICS0058</t>
+  </si>
+  <si>
+    <t>CRTU760967 /9</t>
+  </si>
+  <si>
+    <t>FLAT</t>
+  </si>
+  <si>
+    <t>MSCU255953 /0</t>
+  </si>
+  <si>
+    <t>FJ25931782</t>
+  </si>
+  <si>
+    <t>MSDU600819 /0</t>
+  </si>
+  <si>
+    <t>FJ25931784</t>
+  </si>
+  <si>
+    <t>MSDU749894 /0</t>
+  </si>
+  <si>
+    <t>FJ25931785</t>
+  </si>
+  <si>
+    <t>TCLU600116 /8</t>
+  </si>
+  <si>
+    <t>MSNU975917 /4</t>
+  </si>
+  <si>
+    <t>00005-520-31</t>
   </si>
 </sst>
 </file>
@@ -488,7 +663,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -596,6 +771,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -785,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -927,33 +1109,48 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -963,17 +1160,20 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1256,6 +1456,116 @@
         <a:xfrm>
           <a:off x="76200" y="0"/>
           <a:ext cx="2000250" cy="533397"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEA8FB49-65EA-4CB3-9802-6148FD04982E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="485775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BB04293-D7FF-441C-A0B4-275974B8DEE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1656,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4">
-        <f>B2+C2</f>
+        <f t="shared" ref="D2:D7" si="0">B2+C2</f>
         <v>1</v>
       </c>
       <c r="F2" s="3"/>
@@ -1674,7 +1984,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="4">
-        <f>B3+C3</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="F3" s="3"/>
@@ -1692,7 +2002,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="4">
-        <f>B4+C4</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F4" s="3"/>
@@ -1710,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>B5+C5</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="F5" s="3"/>
@@ -1728,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>B6+C6</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="F6" s="3"/>
@@ -1737,44 +2047,108 @@
       <c r="A7" s="2">
         <v>46303</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="3">
+        <f>'08-10'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <f>'08-10'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B8" s="3">
+        <f>'11-10'!H1</f>
+        <v>16</v>
+      </c>
+      <c r="C8" s="3">
+        <f>'11-10'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" ref="D8:D12" si="1">B8+C8</f>
+        <v>18</v>
+      </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B9" s="3">
+        <f>'08-10'!H3</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <f>'08-10'!H4</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
+      <c r="A10" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B10" s="3">
+        <f>'08-10'!H4</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <f>'08-10'!H5</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B11" s="3">
+        <f>'08-10'!H5</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <f>'08-10'!H6</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B12" s="3">
+        <f>'08-10'!H6</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <f>'08-10'!H7</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -1860,15 +2234,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D19)</f>
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1927,16 +2301,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2486,16 +2860,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3069,16 +3443,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3702,16 +4076,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3753,19 +4127,19 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="63" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
         <v>6102026</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="52" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="53" t="s">
         <v>35</v>
       </c>
       <c r="G8" s="20"/>
@@ -3774,17 +4148,17 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="59"/>
+      <c r="B9" s="64"/>
       <c r="C9" s="19">
         <v>6102026</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="E9" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="52" t="s">
+      <c r="F9" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="20"/>
@@ -3793,17 +4167,17 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="59"/>
+      <c r="B10" s="64"/>
       <c r="C10" s="19">
         <v>6102026</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="F10" s="52" t="s">
+      <c r="F10" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="20"/>
@@ -3812,17 +4186,17 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="59"/>
+      <c r="B11" s="64"/>
       <c r="C11" s="19">
         <v>6102026</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="F11" s="52" t="s">
+      <c r="F11" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="20"/>
@@ -3831,15 +4205,15 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="52" t="s">
+      <c r="B12" s="64"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G12" s="20"/>
@@ -3848,15 +4222,15 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="52" t="s">
+      <c r="B13" s="64"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="56" t="s">
+      <c r="E13" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="52" t="s">
+      <c r="F13" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="20"/>
@@ -3865,15 +4239,15 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="52" t="s">
+      <c r="B14" s="64"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G14" s="20"/>
@@ -3882,17 +4256,17 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="59"/>
+      <c r="B15" s="64"/>
       <c r="C15" s="19">
         <v>6102026</v>
       </c>
-      <c r="D15" s="57" t="s">
+      <c r="D15" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="56" t="s">
+      <c r="E15" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="52" t="s">
+      <c r="F15" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G15" s="20"/>
@@ -3901,15 +4275,15 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="57" t="s">
+      <c r="B16" s="64"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="F16" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="20"/>
@@ -3918,17 +4292,17 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="59"/>
+      <c r="B17" s="64"/>
       <c r="C17" s="19">
         <v>6102026</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="56" t="s">
+      <c r="E17" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="F17" s="52" t="s">
+      <c r="F17" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="20"/>
@@ -3937,15 +4311,15 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="59"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="52" t="s">
+      <c r="B18" s="64"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="F18" s="52" t="s">
+      <c r="F18" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G18" s="20"/>
@@ -3954,17 +4328,17 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="59"/>
+      <c r="B19" s="64"/>
       <c r="C19" s="19">
         <v>6102026</v>
       </c>
-      <c r="D19" s="52" t="s">
+      <c r="D19" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="E19" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="F19" s="52" t="s">
+      <c r="F19" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G19" s="20"/>
@@ -3973,15 +4347,15 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="52" t="s">
+      <c r="B20" s="64"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="20"/>
@@ -3990,15 +4364,15 @@
       <c r="A21" s="17">
         <v>14</v>
       </c>
-      <c r="B21" s="59"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="52" t="s">
+      <c r="B21" s="64"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="52" t="s">
+      <c r="E21" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="F21" s="52" t="s">
+      <c r="F21" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="20"/>
@@ -4007,15 +4381,15 @@
       <c r="A22" s="17">
         <v>15</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="52" t="s">
+      <c r="B22" s="64"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="52" t="s">
+      <c r="E22" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="52" t="s">
+      <c r="F22" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="20"/>
@@ -4024,15 +4398,15 @@
       <c r="A23" s="17">
         <v>16</v>
       </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="57" t="s">
+      <c r="B23" s="64"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="57" t="s">
+      <c r="E23" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="F23" s="52" t="s">
+      <c r="F23" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G23" s="20"/>
@@ -4041,17 +4415,17 @@
       <c r="A24" s="17">
         <v>17</v>
       </c>
-      <c r="B24" s="59"/>
+      <c r="B24" s="64"/>
       <c r="C24" s="19">
         <v>6102026</v>
       </c>
-      <c r="D24" s="57" t="s">
+      <c r="D24" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="52" t="s">
+      <c r="F24" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G24" s="20"/>
@@ -4060,17 +4434,17 @@
       <c r="A25" s="17">
         <v>18</v>
       </c>
-      <c r="B25" s="59"/>
+      <c r="B25" s="64"/>
       <c r="C25" s="19">
         <v>6102026</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="F25" s="52" t="s">
+      <c r="F25" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G25" s="20"/>
@@ -4079,17 +4453,17 @@
       <c r="A26" s="17">
         <v>19</v>
       </c>
-      <c r="B26" s="59"/>
+      <c r="B26" s="64"/>
       <c r="C26" s="19">
         <v>6102026</v>
       </c>
-      <c r="D26" s="57" t="s">
+      <c r="D26" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="F26" s="52" t="s">
+      <c r="F26" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G26" s="20"/>
@@ -4098,17 +4472,17 @@
       <c r="A27" s="17">
         <v>20</v>
       </c>
-      <c r="B27" s="59"/>
+      <c r="B27" s="64"/>
       <c r="C27" s="19">
         <v>6102026</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="52" t="s">
+      <c r="F27" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G27" s="20"/>
@@ -4117,15 +4491,15 @@
       <c r="A28" s="17">
         <v>21</v>
       </c>
-      <c r="B28" s="59"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="57" t="s">
+      <c r="B28" s="64"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="F28" s="52" t="s">
+      <c r="F28" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G28" s="20"/>
@@ -4134,17 +4508,17 @@
       <c r="A29" s="17">
         <v>22</v>
       </c>
-      <c r="B29" s="59"/>
+      <c r="B29" s="64"/>
       <c r="C29" s="19">
         <v>6102026</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="F29" s="52" t="s">
+      <c r="F29" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="20"/>
@@ -4153,17 +4527,17 @@
       <c r="A30" s="17">
         <v>23</v>
       </c>
-      <c r="B30" s="59"/>
+      <c r="B30" s="64"/>
       <c r="C30" s="19">
         <v>6102026</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="52" t="s">
+      <c r="F30" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G30" s="20"/>
@@ -4172,28 +4546,28 @@
       <c r="A31" s="17">
         <v>24</v>
       </c>
-      <c r="B31" s="60"/>
+      <c r="B31" s="65"/>
       <c r="C31" s="19">
         <v>6102026</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="E31" s="57" t="s">
+      <c r="E31" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="52" t="s">
+      <c r="F31" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="50"/>
+      <c r="B32" s="49"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="49"/>
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4408,16 +4782,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4459,7 +4833,7 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="66" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -4480,7 +4854,7 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="63"/>
+      <c r="B9" s="66"/>
       <c r="C9" s="19">
         <v>7102026</v>
       </c>
@@ -4499,7 +4873,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="63"/>
+      <c r="B10" s="66"/>
       <c r="C10" s="19">
         <v>7102026</v>
       </c>
@@ -4518,7 +4892,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="63"/>
+      <c r="B11" s="66"/>
       <c r="C11" s="19">
         <v>7102026</v>
       </c>
@@ -4537,7 +4911,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="63"/>
+      <c r="B12" s="66"/>
       <c r="C12" s="19">
         <v>7102026</v>
       </c>
@@ -4556,7 +4930,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="63"/>
+      <c r="B13" s="66"/>
       <c r="C13" s="19">
         <v>7102026</v>
       </c>
@@ -4575,7 +4949,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="63"/>
+      <c r="B14" s="66"/>
       <c r="C14" s="19">
         <v>7102026</v>
       </c>
@@ -4594,7 +4968,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="63"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="19">
         <v>7102026</v>
       </c>
@@ -4613,7 +4987,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="63"/>
+      <c r="B16" s="66"/>
       <c r="C16" s="19">
         <v>7102026</v>
       </c>
@@ -4632,7 +5006,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="63"/>
+      <c r="B17" s="66"/>
       <c r="C17" s="19">
         <v>7102026</v>
       </c>
@@ -4651,7 +5025,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="66" t="s">
         <v>137</v>
       </c>
       <c r="C18" s="19">
@@ -4672,7 +5046,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="63"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="19">
         <v>7102026</v>
       </c>
@@ -4699,30 +5073,30 @@
       <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="50"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="49"/>
       <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="50"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="49"/>
       <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
-      <c r="B23" s="50"/>
+      <c r="B23" s="49"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="49"/>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4932,4 +5306,1257 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66996BBB-470D-48FB-B1B2-4DB920CC2013}">
+  <dimension ref="A1:M40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C19,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B26:B30,"&lt;&gt;",C26:C30,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C26:C30)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E26:E30,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="58"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="58"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="58"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="58"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="58"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>11</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>12</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>13</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>1</v>
+      </c>
+      <c r="B26" s="19">
+        <v>8102026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="31">
+        <v>3619</v>
+      </c>
+      <c r="F26" s="31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>2</v>
+      </c>
+      <c r="B27" s="19">
+        <v>8102026</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" s="32">
+        <v>3625</v>
+      </c>
+      <c r="F27" s="28">
+        <v>40</v>
+      </c>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>3</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="29"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>4</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="29"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>5</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="29"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="37"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>8102026</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35" s="31">
+        <v>0</v>
+      </c>
+      <c r="F35" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19">
+        <v>8102026</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E36" s="31">
+        <v>3628</v>
+      </c>
+      <c r="F36" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19">
+        <v>8102026</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="31">
+        <v>3627</v>
+      </c>
+      <c r="F37" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>4</v>
+      </c>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="60"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>5</v>
+      </c>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>6</v>
+      </c>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F22" xr:uid="{F2DFE3B4-6C0D-4702-A341-D78DBAF09A0B}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F9277F-0531-4D8C-A730-2360DF7F6B9D}">
+  <dimension ref="A1:M43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C23,"&lt;&gt;")</f>
+        <v>16</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B29:B33,"&lt;&gt;",C29:C33,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C29:C33)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E29:E33,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="68"/>
+      <c r="C11" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="68"/>
+      <c r="C12" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="68"/>
+      <c r="C13" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="68"/>
+      <c r="C14" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="69"/>
+      <c r="C15" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>10</v>
+      </c>
+      <c r="B17" s="68"/>
+      <c r="C17" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>11</v>
+      </c>
+      <c r="B18" s="68"/>
+      <c r="C18" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>12</v>
+      </c>
+      <c r="B19" s="68"/>
+      <c r="C19" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="28">
+        <v>13</v>
+      </c>
+      <c r="B20" s="68"/>
+      <c r="C20" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="28">
+        <v>14</v>
+      </c>
+      <c r="B21" s="69"/>
+      <c r="C21" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="28">
+        <v>15</v>
+      </c>
+      <c r="B22" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="28">
+        <v>16</v>
+      </c>
+      <c r="B23" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="37"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="20"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>1</v>
+      </c>
+      <c r="B29" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="31">
+        <v>3626</v>
+      </c>
+      <c r="F29" s="31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>2</v>
+      </c>
+      <c r="B30" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="E30" s="32">
+        <v>3705</v>
+      </c>
+      <c r="F30" s="28">
+        <v>40</v>
+      </c>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>3</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="29"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28">
+        <v>4</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="29"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28">
+        <v>5</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="29"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="37"/>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>1</v>
+      </c>
+      <c r="B38" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="E38" s="32">
+        <v>0</v>
+      </c>
+      <c r="F38" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>2</v>
+      </c>
+      <c r="B39" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" s="32">
+        <v>3671</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>3</v>
+      </c>
+      <c r="B40" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="E40" s="32">
+        <v>3630</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>4</v>
+      </c>
+      <c r="B41" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" s="32">
+        <v>3629</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="28">
+        <v>5</v>
+      </c>
+      <c r="B42" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="E42" s="32">
+        <v>0</v>
+      </c>
+      <c r="F42" s="28">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="28">
+        <v>6</v>
+      </c>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="B16:B21"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F25 F38:F42" xr:uid="{59A1728A-5F57-40ED-BA5C-963023DC64E0}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0AB0B5A2ED962CAE/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{268A7E5D-2F6F-4219-A3FF-0CDC0150617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4669A96C-1B39-4554-A9F9-24A8525A00D0}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{268A7E5D-2F6F-4219-A3FF-0CDC0150617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12651A1A-ECE6-427F-9AD0-CE2F5712D9DC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" activeTab="7" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" activeTab="8" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="07-10" sheetId="6" r:id="rId6"/>
     <sheet name="08-10" sheetId="7" r:id="rId7"/>
     <sheet name="11-10" sheetId="8" r:id="rId8"/>
+    <sheet name="12-10" sheetId="9" r:id="rId9"/>
+    <sheet name="13-10" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="210">
   <si>
     <t>Date</t>
   </si>
@@ -653,6 +655,30 @@
   </si>
   <si>
     <t>00005-520-31</t>
+  </si>
+  <si>
+    <t>02175-588-31</t>
+  </si>
+  <si>
+    <t>TIIU809713 /9</t>
+  </si>
+  <si>
+    <t>M1726190</t>
+  </si>
+  <si>
+    <t>MSDU612394 /9</t>
+  </si>
+  <si>
+    <t>TCKU725483 /6</t>
+  </si>
+  <si>
+    <t>BD0235592</t>
+  </si>
+  <si>
+    <t>00235-509-31</t>
+  </si>
+  <si>
+    <t>OOCU568279 /5</t>
   </si>
 </sst>
 </file>
@@ -761,16 +787,19 @@
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -967,7 +996,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1148,7 +1177,19 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1163,17 +1204,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1577,6 +1609,120 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF59B7B3-F4C9-42B7-B149-82B3A9E7D13E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="485775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41FBF36A-3D19-4FFB-8D35-F7087D29E1F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="485775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2071,11 +2217,11 @@
       </c>
       <c r="C8" s="3">
         <f>'11-10'!H2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" ref="D8:D12" si="1">B8+C8</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" s="3"/>
     </row>
@@ -2084,16 +2230,16 @@
         <v>46307</v>
       </c>
       <c r="B9" s="3">
-        <f>'08-10'!H3</f>
+        <f>'12-10'!H1</f>
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <f>'08-10'!H4</f>
-        <v>0</v>
+        <f>'12-10'!H2</f>
+        <v>1</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -2102,11 +2248,11 @@
         <v>46308</v>
       </c>
       <c r="B10" s="3">
-        <f>'08-10'!H4</f>
+        <f>'13-10'!H1</f>
         <v>0</v>
       </c>
       <c r="C10" s="3">
-        <f>'08-10'!H5</f>
+        <f>'13-10'!H2</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
@@ -2238,17 +2384,499 @@
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D19)</f>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA60AB76-816B-4073-971C-3BEE45E25848}">
+  <dimension ref="A1:M40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C19,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B26:B30,"&lt;&gt;",C26:C30,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C26:C30)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E26:E30,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="58"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="58"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="58"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="58"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="58"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>11</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>12</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>13</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>1</v>
+      </c>
+      <c r="B26" s="19">
+        <v>8102026</v>
+      </c>
+      <c r="C26" s="29"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>2</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="28"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>3</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="29"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>4</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="29"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>5</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="29"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="37"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>8102026</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="41"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="41"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="41"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>4</v>
+      </c>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="60"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>5</v>
+      </c>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>6</v>
+      </c>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F22" xr:uid="{8FFE6855-E471-46A7-B099-99631BE7F1A1}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2301,16 +2929,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2860,16 +3488,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3443,16 +4071,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4076,16 +4704,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4127,7 +4755,7 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="67" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -4148,7 +4776,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="64"/>
+      <c r="B9" s="68"/>
       <c r="C9" s="19">
         <v>6102026</v>
       </c>
@@ -4167,7 +4795,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="64"/>
+      <c r="B10" s="68"/>
       <c r="C10" s="19">
         <v>6102026</v>
       </c>
@@ -4186,7 +4814,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="64"/>
+      <c r="B11" s="68"/>
       <c r="C11" s="19">
         <v>6102026</v>
       </c>
@@ -4205,7 +4833,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="64"/>
+      <c r="B12" s="68"/>
       <c r="C12" s="57"/>
       <c r="D12" s="51" t="s">
         <v>125</v>
@@ -4222,7 +4850,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="64"/>
+      <c r="B13" s="68"/>
       <c r="C13" s="57"/>
       <c r="D13" s="51" t="s">
         <v>123</v>
@@ -4239,7 +4867,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="64"/>
+      <c r="B14" s="68"/>
       <c r="C14" s="57"/>
       <c r="D14" s="51" t="s">
         <v>121</v>
@@ -4256,7 +4884,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="64"/>
+      <c r="B15" s="68"/>
       <c r="C15" s="19">
         <v>6102026</v>
       </c>
@@ -4275,7 +4903,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="64"/>
+      <c r="B16" s="68"/>
       <c r="C16" s="57"/>
       <c r="D16" s="56" t="s">
         <v>117</v>
@@ -4292,7 +4920,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="64"/>
+      <c r="B17" s="68"/>
       <c r="C17" s="19">
         <v>6102026</v>
       </c>
@@ -4311,7 +4939,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="64"/>
+      <c r="B18" s="68"/>
       <c r="C18" s="57"/>
       <c r="D18" s="51" t="s">
         <v>113</v>
@@ -4328,7 +4956,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="64"/>
+      <c r="B19" s="68"/>
       <c r="C19" s="19">
         <v>6102026</v>
       </c>
@@ -4347,7 +4975,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="64"/>
+      <c r="B20" s="68"/>
       <c r="C20" s="57"/>
       <c r="D20" s="51" t="s">
         <v>109</v>
@@ -4364,7 +4992,7 @@
       <c r="A21" s="17">
         <v>14</v>
       </c>
-      <c r="B21" s="64"/>
+      <c r="B21" s="68"/>
       <c r="C21" s="57"/>
       <c r="D21" s="51" t="s">
         <v>107</v>
@@ -4381,7 +5009,7 @@
       <c r="A22" s="17">
         <v>15</v>
       </c>
-      <c r="B22" s="64"/>
+      <c r="B22" s="68"/>
       <c r="C22" s="57"/>
       <c r="D22" s="51" t="s">
         <v>105</v>
@@ -4398,7 +5026,7 @@
       <c r="A23" s="17">
         <v>16</v>
       </c>
-      <c r="B23" s="64"/>
+      <c r="B23" s="68"/>
       <c r="C23" s="57"/>
       <c r="D23" s="56" t="s">
         <v>103</v>
@@ -4415,7 +5043,7 @@
       <c r="A24" s="17">
         <v>17</v>
       </c>
-      <c r="B24" s="64"/>
+      <c r="B24" s="68"/>
       <c r="C24" s="19">
         <v>6102026</v>
       </c>
@@ -4434,7 +5062,7 @@
       <c r="A25" s="17">
         <v>18</v>
       </c>
-      <c r="B25" s="64"/>
+      <c r="B25" s="68"/>
       <c r="C25" s="19">
         <v>6102026</v>
       </c>
@@ -4453,7 +5081,7 @@
       <c r="A26" s="17">
         <v>19</v>
       </c>
-      <c r="B26" s="64"/>
+      <c r="B26" s="68"/>
       <c r="C26" s="19">
         <v>6102026</v>
       </c>
@@ -4472,7 +5100,7 @@
       <c r="A27" s="17">
         <v>20</v>
       </c>
-      <c r="B27" s="64"/>
+      <c r="B27" s="68"/>
       <c r="C27" s="19">
         <v>6102026</v>
       </c>
@@ -4491,7 +5119,7 @@
       <c r="A28" s="17">
         <v>21</v>
       </c>
-      <c r="B28" s="64"/>
+      <c r="B28" s="68"/>
       <c r="C28" s="57"/>
       <c r="D28" s="56" t="s">
         <v>93</v>
@@ -4508,7 +5136,7 @@
       <c r="A29" s="17">
         <v>22</v>
       </c>
-      <c r="B29" s="64"/>
+      <c r="B29" s="68"/>
       <c r="C29" s="19">
         <v>6102026</v>
       </c>
@@ -4527,7 +5155,7 @@
       <c r="A30" s="17">
         <v>23</v>
       </c>
-      <c r="B30" s="64"/>
+      <c r="B30" s="68"/>
       <c r="C30" s="19">
         <v>6102026</v>
       </c>
@@ -4546,7 +5174,7 @@
       <c r="A31" s="17">
         <v>24</v>
       </c>
-      <c r="B31" s="65"/>
+      <c r="B31" s="69"/>
       <c r="C31" s="19">
         <v>6102026</v>
       </c>
@@ -4782,16 +5410,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4833,7 +5461,7 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="70" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -4854,7 +5482,7 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="66"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="19">
         <v>7102026</v>
       </c>
@@ -4873,7 +5501,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="66"/>
+      <c r="B10" s="70"/>
       <c r="C10" s="19">
         <v>7102026</v>
       </c>
@@ -4892,7 +5520,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="66"/>
+      <c r="B11" s="70"/>
       <c r="C11" s="19">
         <v>7102026</v>
       </c>
@@ -4911,7 +5539,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="66"/>
+      <c r="B12" s="70"/>
       <c r="C12" s="19">
         <v>7102026</v>
       </c>
@@ -4930,7 +5558,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="66"/>
+      <c r="B13" s="70"/>
       <c r="C13" s="19">
         <v>7102026</v>
       </c>
@@ -4949,7 +5577,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="66"/>
+      <c r="B14" s="70"/>
       <c r="C14" s="19">
         <v>7102026</v>
       </c>
@@ -4968,7 +5596,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="66"/>
+      <c r="B15" s="70"/>
       <c r="C15" s="19">
         <v>7102026</v>
       </c>
@@ -4987,7 +5615,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="66"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="19">
         <v>7102026</v>
       </c>
@@ -5006,7 +5634,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="66"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="19">
         <v>7102026</v>
       </c>
@@ -5025,7 +5653,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="70" t="s">
         <v>137</v>
       </c>
       <c r="C18" s="19">
@@ -5046,7 +5674,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="66"/>
+      <c r="B19" s="70"/>
       <c r="C19" s="19">
         <v>7102026</v>
       </c>
@@ -5357,16 +5985,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5831,8 +6459,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5874,7 +6503,7 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C29:C33)-F2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
@@ -5885,16 +6514,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5978,7 +6607,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="64" t="s">
         <v>187</v>
       </c>
       <c r="C10" s="19">
@@ -5999,7 +6628,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="68"/>
+      <c r="B11" s="65"/>
       <c r="C11" s="19">
         <v>11102026</v>
       </c>
@@ -6018,7 +6647,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="68"/>
+      <c r="B12" s="65"/>
       <c r="C12" s="19">
         <v>11102026</v>
       </c>
@@ -6037,7 +6666,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="68"/>
+      <c r="B13" s="65"/>
       <c r="C13" s="19">
         <v>11102026</v>
       </c>
@@ -6056,7 +6685,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="68"/>
+      <c r="B14" s="65"/>
       <c r="C14" s="19">
         <v>11102026</v>
       </c>
@@ -6075,7 +6704,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="69"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="19">
         <v>11102026</v>
       </c>
@@ -6094,7 +6723,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="64" t="s">
         <v>188</v>
       </c>
       <c r="C16" s="19">
@@ -6115,7 +6744,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="68"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="19">
         <v>11102026</v>
       </c>
@@ -6134,7 +6763,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="68"/>
+      <c r="B18" s="65"/>
       <c r="C18" s="19">
         <v>11102026</v>
       </c>
@@ -6153,7 +6782,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="68"/>
+      <c r="B19" s="65"/>
       <c r="C19" s="19">
         <v>11102026</v>
       </c>
@@ -6172,7 +6801,7 @@
       <c r="A20" s="28">
         <v>13</v>
       </c>
-      <c r="B20" s="68"/>
+      <c r="B20" s="65"/>
       <c r="C20" s="19">
         <v>11102026</v>
       </c>
@@ -6191,7 +6820,7 @@
       <c r="A21" s="28">
         <v>14</v>
       </c>
-      <c r="B21" s="69"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="19">
         <v>11102026</v>
       </c>
@@ -6252,8 +6881,8 @@
       <c r="A24" s="37"/>
       <c r="B24" s="37"/>
       <c r="C24" s="38"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
       <c r="F24" s="37"/>
       <c r="G24" s="20"/>
     </row>
@@ -6349,11 +6978,21 @@
       <c r="A31" s="28">
         <v>3</v>
       </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="29"/>
+      <c r="B31" s="19">
+        <v>11102026</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="31">
+        <v>3620</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>35</v>
+      </c>
       <c r="I31" s="33"/>
       <c r="J31" s="33"/>
       <c r="K31" s="33"/>
@@ -6551,12 +7190,542 @@
     <mergeCell ref="B16:B21"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F25 F38:F42" xr:uid="{59A1728A-5F57-40ED-BA5C-963023DC64E0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F25 F38:F42 F31" xr:uid="{59A1728A-5F57-40ED-BA5C-963023DC64E0}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0609E17-8CE5-470B-81E0-265695749A6F}">
+  <dimension ref="A1:M40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C19,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B26:B30,"&lt;&gt;",C26:C30,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C26:C30)-F2</f>
+        <v>1</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E26:E30,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="58"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="58"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="58"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="58"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="58"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>11</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>12</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>13</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>1</v>
+      </c>
+      <c r="B26" s="19">
+        <v>12102026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="E26" s="71">
+        <v>32460820</v>
+      </c>
+      <c r="F26" s="59">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>2</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="28"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>3</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="29"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>4</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="29"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>5</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="29"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="37"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>12102026</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D35" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="E35" s="31">
+        <v>3672</v>
+      </c>
+      <c r="F35" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19">
+        <v>12102026</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36" s="30">
+        <v>2139541</v>
+      </c>
+      <c r="E36" s="31">
+        <v>3673</v>
+      </c>
+      <c r="F36" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19">
+        <v>12102026</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" s="31">
+        <v>3674</v>
+      </c>
+      <c r="F37" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19">
+        <v>12102026</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38" s="31">
+        <v>3673</v>
+      </c>
+      <c r="E38" s="47">
+        <v>3675</v>
+      </c>
+      <c r="F38" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>5</v>
+      </c>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>6</v>
+      </c>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F22" xr:uid="{7525A792-665F-4247-9C0B-045671E982E8}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0AB0B5A2ED962CAE/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{268A7E5D-2F6F-4219-A3FF-0CDC0150617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12651A1A-ECE6-427F-9AD0-CE2F5712D9DC}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7AB298-B024-40A8-BF85-21CB00CDB44D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" activeTab="8" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="11-10" sheetId="8" r:id="rId8"/>
     <sheet name="12-10" sheetId="9" r:id="rId9"/>
     <sheet name="13-10" sheetId="10" r:id="rId10"/>
+    <sheet name="14-10" sheetId="11" r:id="rId11"/>
+    <sheet name="15-10" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="247">
   <si>
     <t>Date</t>
   </si>
@@ -679,6 +681,117 @@
   </si>
   <si>
     <t>OOCU568279 /5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMAU229574 /9 </t>
+  </si>
+  <si>
+    <t>M7399417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMAU238193 /4 </t>
+  </si>
+  <si>
+    <t>M7399419</t>
+  </si>
+  <si>
+    <t>ECMU294199 /1</t>
+  </si>
+  <si>
+    <t>M7399384</t>
+  </si>
+  <si>
+    <t>ECMU295618 /4</t>
+  </si>
+  <si>
+    <t>M7399466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMU032969 /2 </t>
+  </si>
+  <si>
+    <t>M7349446</t>
+  </si>
+  <si>
+    <t>TCLU9579756</t>
+  </si>
+  <si>
+    <t>M1653661</t>
+  </si>
+  <si>
+    <t>TXGU4968523</t>
+  </si>
+  <si>
+    <t>FJ28506777</t>
+  </si>
+  <si>
+    <t>CAIU7122168</t>
+  </si>
+  <si>
+    <t>FJ28489616</t>
+  </si>
+  <si>
+    <t>0869ICS0102</t>
+  </si>
+  <si>
+    <t>0181ICS0146</t>
+  </si>
+  <si>
+    <t>0181ICS0030</t>
+  </si>
+  <si>
+    <t>TCNU338016 /8</t>
+  </si>
+  <si>
+    <t>CMAU965494 /3</t>
+  </si>
+  <si>
+    <t>FX33492438</t>
+  </si>
+  <si>
+    <t>00204-598-31</t>
+  </si>
+  <si>
+    <t>TCNU628382 /9</t>
+  </si>
+  <si>
+    <t>00139-513-31</t>
+  </si>
+  <si>
+    <t>UETU7239787</t>
+  </si>
+  <si>
+    <t>972218</t>
+  </si>
+  <si>
+    <t>TRHU7683171</t>
+  </si>
+  <si>
+    <t>972213</t>
+  </si>
+  <si>
+    <t>MSMU7919393</t>
+  </si>
+  <si>
+    <t>FX49468610</t>
+  </si>
+  <si>
+    <t>BMOU6940792</t>
+  </si>
+  <si>
+    <t>FX48529707</t>
+  </si>
+  <si>
+    <t>0892ICS0085</t>
+  </si>
+  <si>
+    <t>0892ICS0087</t>
+  </si>
+  <si>
+    <t>0182ICS0024</t>
+  </si>
+  <si>
+    <t>0182ICS0041</t>
   </si>
 </sst>
 </file>
@@ -689,7 +802,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -804,6 +917,12 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -996,7 +1115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1180,16 +1299,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1204,8 +1320,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1268,6 +1390,116 @@
         <a:xfrm>
           <a:off x="180975" y="0"/>
           <a:ext cx="2000250" cy="495297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{873EF647-D77E-40A3-B524-61B41D808079}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F12FD6AF-C560-4CFF-95D7-300E7F5E35AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="523875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1719,10 +1951,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2070,6 +2298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B954E8F3-6789-4A30-A0C0-D561ABF2356F}">
+  <sheetPr codeName="Feuil1"/>
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2122,11 +2351,11 @@
         <v>46299</v>
       </c>
       <c r="B3" s="3">
-        <f>'04-10'!J1</f>
+        <f>'04-10'!H1</f>
         <v>5</v>
       </c>
       <c r="C3" s="3">
-        <f>'04-10'!J2</f>
+        <f>'04-10'!H2</f>
         <v>3</v>
       </c>
       <c r="D3" s="4">
@@ -2220,7 +2449,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:D12" si="1">B8+C8</f>
+        <f>B8+C8</f>
         <v>19</v>
       </c>
       <c r="F8" s="3"/>
@@ -2238,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="1"/>
+        <f>B9+C9</f>
         <v>1</v>
       </c>
       <c r="F9" s="3"/>
@@ -2249,15 +2478,15 @@
       </c>
       <c r="B10" s="3">
         <f>'13-10'!H1</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3">
         <f>'13-10'!H2</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>B10+C10</f>
+        <v>3</v>
       </c>
       <c r="F10" s="3"/>
     </row>
@@ -2266,16 +2495,16 @@
         <v>46309</v>
       </c>
       <c r="B11" s="3">
-        <f>'08-10'!H5</f>
+        <f>'14-10'!H1</f>
         <v>0</v>
       </c>
       <c r="C11" s="3">
-        <f>'08-10'!H6</f>
-        <v>0</v>
+        <f>'14-10'!H2</f>
+        <v>3</v>
       </c>
       <c r="D11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>B11+C11</f>
+        <v>3</v>
       </c>
       <c r="F11" s="3"/>
     </row>
@@ -2284,16 +2513,16 @@
         <v>46310</v>
       </c>
       <c r="B12" s="3">
-        <f>'08-10'!H6</f>
+        <f>'15-10'!H1</f>
+        <v>4</v>
+      </c>
+      <c r="C12" s="3">
+        <f>'15-10'!H2</f>
         <v>0</v>
       </c>
-      <c r="C12" s="3">
-        <f>'08-10'!H7</f>
-        <v>0</v>
-      </c>
       <c r="D12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>B12+C12</f>
+        <v>4</v>
       </c>
       <c r="F12" s="3"/>
     </row>
@@ -2380,15 +2609,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D19)</f>
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -2400,6 +2629,601 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA60AB76-816B-4073-971C-3BEE45E25848}">
+  <sheetPr codeName="Feuil10"/>
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C19,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B26:B30,"&lt;&gt;",C26:C30,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C26:C30)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E26:E30,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="58"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="58"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="58"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>11</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>12</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>13</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>1</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>2</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="28"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>3</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="29"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>4</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="29"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>5</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="29"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="37"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" s="28">
+        <v>3676</v>
+      </c>
+      <c r="F35" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="E36" s="28">
+        <v>3677</v>
+      </c>
+      <c r="F36" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" s="28">
+        <v>3678</v>
+      </c>
+      <c r="F37" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="D38" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="E38" s="28">
+        <v>3679</v>
+      </c>
+      <c r="F38" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E39" s="28">
+        <v>3680</v>
+      </c>
+      <c r="F39" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="E40" s="31">
+        <v>3729</v>
+      </c>
+      <c r="F40" s="31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19">
+        <v>13102026</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="D41" s="31">
+        <v>40680147</v>
+      </c>
+      <c r="E41" s="28">
+        <v>3730</v>
+      </c>
+      <c r="F41" s="28">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F22" xr:uid="{8FFE6855-E471-46A7-B099-99631BE7F1A1}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35:F39 F41" xr:uid="{1EB1E177-F6E0-4B47-BCA3-D3921ED772AB}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4D7A86-522F-43B1-845A-460AE7832055}">
+  <sheetPr codeName="Feuil11"/>
   <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2436,7 +3260,7 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C26:C30)-F2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
@@ -2447,16 +3271,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2467,7 +3291,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="12">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2498,33 +3322,33 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="58"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="19"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="28"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="24"/>
       <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="58"/>
+      <c r="B9" s="64"/>
       <c r="C9" s="19"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="28"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
       <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="58"/>
+      <c r="B10" s="64"/>
       <c r="C10" s="19"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="28"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2692,12 +3516,584 @@
         <v>1</v>
       </c>
       <c r="B26" s="19">
-        <v>8102026</v>
+        <v>14102026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="41">
+        <v>3624</v>
+      </c>
+      <c r="F26" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>2</v>
+      </c>
+      <c r="B27" s="19">
+        <v>14102026</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" s="31">
+        <v>3672</v>
+      </c>
+      <c r="F27" s="28">
+        <v>40</v>
+      </c>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>3</v>
+      </c>
+      <c r="B28" s="19">
+        <v>14102026</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="E28" s="31">
+        <v>3613</v>
+      </c>
+      <c r="F28" s="24">
+        <v>45</v>
+      </c>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>4</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="29"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>5</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="29"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="37"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>14102026</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" s="31">
+        <v>3728</v>
+      </c>
+      <c r="F35" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19">
+        <v>14102026</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="28">
+        <v>5878917</v>
+      </c>
+      <c r="E36" s="28">
+        <v>3727</v>
+      </c>
+      <c r="F36" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>6</v>
+      </c>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35:F39" xr:uid="{62C6AADC-B5D7-445F-9999-F8E7F6CC9310}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F22 F28" xr:uid="{F6098247-211A-4381-B194-8E72608F756F}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8E4176-44D6-4CE5-8273-4AB7EA8EE430}">
+  <dimension ref="A1:M40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C19,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B26:B30,"&lt;&gt;",C26:C30,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C26:C30)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E26:E30,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="58"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="58"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>11</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>12</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>13</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>1</v>
+      </c>
+      <c r="B26" s="19">
+        <v>15102026</v>
       </c>
       <c r="C26" s="29"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
@@ -2808,52 +4204,52 @@
         <v>1</v>
       </c>
       <c r="B35" s="19">
-        <v>8102026</v>
-      </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="41"/>
+        <v>15102026</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
         <v>2</v>
       </c>
       <c r="B36" s="19"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="41"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
         <v>3</v>
       </c>
       <c r="B37" s="19"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="41"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <v>4</v>
       </c>
-      <c r="B38" s="59"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="60"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
         <v>5</v>
       </c>
-      <c r="B39" s="59"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="28">
@@ -2869,10 +4265,13 @@
   <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F22" xr:uid="{8FFE6855-E471-46A7-B099-99631BE7F1A1}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F22" xr:uid="{D2398EA4-793A-4429-A19B-C4C1350F4CAE}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35:F39" xr:uid="{37301691-48F1-475D-BF15-1DEF68A23EB3}">
+      <formula1>"20,40,45,50"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2882,6 +4281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6127B32-66FD-4821-B5A5-DCC3BF3FE01D}">
+  <sheetPr codeName="Feuil2"/>
   <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2929,16 +4329,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3441,6 +4841,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85DF543D-4975-46C5-B25F-16F918CE2918}">
+  <sheetPr codeName="Feuil3"/>
   <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3456,53 +4857,53 @@
     <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="J1" s="8">
+      <c r="H1" s="8">
         <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
         <v>5</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="H2" s="8">
+      <c r="F2" s="8">
         <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
         <v>0</v>
       </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>3</v>
+      </c>
       <c r="I2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="8">
-        <f>COUNTA(C20:C29)-H2</f>
-        <v>3</v>
-      </c>
-      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="10">
+      <c r="J2" s="10">
         <f>COUNTIF(E20:E29,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-    </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
@@ -3511,11 +4912,11 @@
         <v>46299</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
@@ -3535,7 +4936,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
@@ -3556,7 +4957,7 @@
       </c>
       <c r="G8" s="20"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
@@ -3577,7 +4978,7 @@
       </c>
       <c r="G9" s="20"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
@@ -3598,7 +4999,7 @@
       </c>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
@@ -3619,7 +5020,7 @@
       </c>
       <c r="G11" s="20"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
@@ -3640,7 +5041,7 @@
       </c>
       <c r="G12" s="20"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
@@ -3651,7 +5052,7 @@
       <c r="F13" s="24"/>
       <c r="G13" s="20"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
@@ -3662,7 +5063,7 @@
       <c r="F14" s="24"/>
       <c r="G14" s="20"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
@@ -3673,7 +5074,7 @@
       <c r="F15" s="24"/>
       <c r="G15" s="20"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="20"/>
       <c r="C16" s="7"/>
@@ -4024,6 +5425,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E68CDFBC-7B67-49C8-BC1D-EC76810F57FF}">
+  <sheetPr codeName="Feuil4"/>
   <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4071,16 +5473,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4657,6 +6059,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A16EF8D-37CA-4A31-8D52-A76DF0BB1357}">
+  <sheetPr codeName="Feuil5"/>
   <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4704,16 +6107,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4755,7 +6158,7 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="66" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -4776,7 +6179,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="68"/>
+      <c r="B9" s="67"/>
       <c r="C9" s="19">
         <v>6102026</v>
       </c>
@@ -4795,7 +6198,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="68"/>
+      <c r="B10" s="67"/>
       <c r="C10" s="19">
         <v>6102026</v>
       </c>
@@ -4814,7 +6217,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="68"/>
+      <c r="B11" s="67"/>
       <c r="C11" s="19">
         <v>6102026</v>
       </c>
@@ -4833,7 +6236,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="68"/>
+      <c r="B12" s="67"/>
       <c r="C12" s="57"/>
       <c r="D12" s="51" t="s">
         <v>125</v>
@@ -4850,7 +6253,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="68"/>
+      <c r="B13" s="67"/>
       <c r="C13" s="57"/>
       <c r="D13" s="51" t="s">
         <v>123</v>
@@ -4867,7 +6270,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="68"/>
+      <c r="B14" s="67"/>
       <c r="C14" s="57"/>
       <c r="D14" s="51" t="s">
         <v>121</v>
@@ -4884,7 +6287,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="68"/>
+      <c r="B15" s="67"/>
       <c r="C15" s="19">
         <v>6102026</v>
       </c>
@@ -4903,7 +6306,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="68"/>
+      <c r="B16" s="67"/>
       <c r="C16" s="57"/>
       <c r="D16" s="56" t="s">
         <v>117</v>
@@ -4920,7 +6323,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="68"/>
+      <c r="B17" s="67"/>
       <c r="C17" s="19">
         <v>6102026</v>
       </c>
@@ -4939,7 +6342,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="68"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="57"/>
       <c r="D18" s="51" t="s">
         <v>113</v>
@@ -4956,7 +6359,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="68"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="19">
         <v>6102026</v>
       </c>
@@ -4975,7 +6378,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="68"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="57"/>
       <c r="D20" s="51" t="s">
         <v>109</v>
@@ -4992,7 +6395,7 @@
       <c r="A21" s="17">
         <v>14</v>
       </c>
-      <c r="B21" s="68"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="57"/>
       <c r="D21" s="51" t="s">
         <v>107</v>
@@ -5009,7 +6412,7 @@
       <c r="A22" s="17">
         <v>15</v>
       </c>
-      <c r="B22" s="68"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="57"/>
       <c r="D22" s="51" t="s">
         <v>105</v>
@@ -5026,7 +6429,7 @@
       <c r="A23" s="17">
         <v>16</v>
       </c>
-      <c r="B23" s="68"/>
+      <c r="B23" s="67"/>
       <c r="C23" s="57"/>
       <c r="D23" s="56" t="s">
         <v>103</v>
@@ -5043,7 +6446,7 @@
       <c r="A24" s="17">
         <v>17</v>
       </c>
-      <c r="B24" s="68"/>
+      <c r="B24" s="67"/>
       <c r="C24" s="19">
         <v>6102026</v>
       </c>
@@ -5062,7 +6465,7 @@
       <c r="A25" s="17">
         <v>18</v>
       </c>
-      <c r="B25" s="68"/>
+      <c r="B25" s="67"/>
       <c r="C25" s="19">
         <v>6102026</v>
       </c>
@@ -5081,7 +6484,7 @@
       <c r="A26" s="17">
         <v>19</v>
       </c>
-      <c r="B26" s="68"/>
+      <c r="B26" s="67"/>
       <c r="C26" s="19">
         <v>6102026</v>
       </c>
@@ -5100,7 +6503,7 @@
       <c r="A27" s="17">
         <v>20</v>
       </c>
-      <c r="B27" s="68"/>
+      <c r="B27" s="67"/>
       <c r="C27" s="19">
         <v>6102026</v>
       </c>
@@ -5119,7 +6522,7 @@
       <c r="A28" s="17">
         <v>21</v>
       </c>
-      <c r="B28" s="68"/>
+      <c r="B28" s="67"/>
       <c r="C28" s="57"/>
       <c r="D28" s="56" t="s">
         <v>93</v>
@@ -5136,7 +6539,7 @@
       <c r="A29" s="17">
         <v>22</v>
       </c>
-      <c r="B29" s="68"/>
+      <c r="B29" s="67"/>
       <c r="C29" s="19">
         <v>6102026</v>
       </c>
@@ -5155,7 +6558,7 @@
       <c r="A30" s="17">
         <v>23</v>
       </c>
-      <c r="B30" s="68"/>
+      <c r="B30" s="67"/>
       <c r="C30" s="19">
         <v>6102026</v>
       </c>
@@ -5174,7 +6577,7 @@
       <c r="A31" s="17">
         <v>24</v>
       </c>
-      <c r="B31" s="69"/>
+      <c r="B31" s="68"/>
       <c r="C31" s="19">
         <v>6102026</v>
       </c>
@@ -5363,6 +6766,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A960496-9B69-4504-85DD-0BDC7520975C}">
+  <sheetPr codeName="Feuil6"/>
   <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5410,16 +6814,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5461,7 +6865,7 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="69" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -5482,7 +6886,7 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="70"/>
+      <c r="B9" s="69"/>
       <c r="C9" s="19">
         <v>7102026</v>
       </c>
@@ -5501,7 +6905,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="70"/>
+      <c r="B10" s="69"/>
       <c r="C10" s="19">
         <v>7102026</v>
       </c>
@@ -5520,7 +6924,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="70"/>
+      <c r="B11" s="69"/>
       <c r="C11" s="19">
         <v>7102026</v>
       </c>
@@ -5539,7 +6943,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="70"/>
+      <c r="B12" s="69"/>
       <c r="C12" s="19">
         <v>7102026</v>
       </c>
@@ -5558,7 +6962,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="70"/>
+      <c r="B13" s="69"/>
       <c r="C13" s="19">
         <v>7102026</v>
       </c>
@@ -5577,7 +6981,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="70"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="19">
         <v>7102026</v>
       </c>
@@ -5596,7 +7000,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="70"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="19">
         <v>7102026</v>
       </c>
@@ -5615,7 +7019,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="70"/>
+      <c r="B16" s="69"/>
       <c r="C16" s="19">
         <v>7102026</v>
       </c>
@@ -5634,7 +7038,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="70"/>
+      <c r="B17" s="69"/>
       <c r="C17" s="19">
         <v>7102026</v>
       </c>
@@ -5653,7 +7057,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="69" t="s">
         <v>137</v>
       </c>
       <c r="C18" s="19">
@@ -5674,7 +7078,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="70"/>
+      <c r="B19" s="69"/>
       <c r="C19" s="19">
         <v>7102026</v>
       </c>
@@ -5938,6 +7342,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66996BBB-470D-48FB-B1B2-4DB920CC2013}">
+  <sheetPr codeName="Feuil7"/>
   <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5985,16 +7390,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6467,6 +7872,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F9277F-0531-4D8C-A730-2360DF7F6B9D}">
+  <sheetPr codeName="Feuil8"/>
   <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6514,16 +7920,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6607,7 +8013,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="70" t="s">
         <v>187</v>
       </c>
       <c r="C10" s="19">
@@ -6628,7 +8034,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="65"/>
+      <c r="B11" s="71"/>
       <c r="C11" s="19">
         <v>11102026</v>
       </c>
@@ -6647,7 +8053,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="65"/>
+      <c r="B12" s="71"/>
       <c r="C12" s="19">
         <v>11102026</v>
       </c>
@@ -6666,7 +8072,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="65"/>
+      <c r="B13" s="71"/>
       <c r="C13" s="19">
         <v>11102026</v>
       </c>
@@ -6685,7 +8091,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="65"/>
+      <c r="B14" s="71"/>
       <c r="C14" s="19">
         <v>11102026</v>
       </c>
@@ -6704,7 +8110,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="66"/>
+      <c r="B15" s="72"/>
       <c r="C15" s="19">
         <v>11102026</v>
       </c>
@@ -6723,7 +8129,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="70" t="s">
         <v>188</v>
       </c>
       <c r="C16" s="19">
@@ -6744,7 +8150,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="65"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="19">
         <v>11102026</v>
       </c>
@@ -6763,7 +8169,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="65"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="19">
         <v>11102026</v>
       </c>
@@ -6782,7 +8188,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="65"/>
+      <c r="B19" s="71"/>
       <c r="C19" s="19">
         <v>11102026</v>
       </c>
@@ -6801,7 +8207,7 @@
       <c r="A20" s="28">
         <v>13</v>
       </c>
-      <c r="B20" s="65"/>
+      <c r="B20" s="71"/>
       <c r="C20" s="19">
         <v>11102026</v>
       </c>
@@ -6820,7 +8226,7 @@
       <c r="A21" s="28">
         <v>14</v>
       </c>
-      <c r="B21" s="66"/>
+      <c r="B21" s="72"/>
       <c r="C21" s="19">
         <v>11102026</v>
       </c>
@@ -7203,6 +8609,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0609E17-8CE5-470B-81E0-265695749A6F}">
+  <sheetPr codeName="Feuil9"/>
   <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7250,16 +8657,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7503,7 +8910,7 @@
       <c r="D26" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="E26" s="71">
+      <c r="E26" s="63">
         <v>32460820</v>
       </c>
       <c r="F26" s="59">

--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0AB0B5A2ED962CAE/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7AB298-B024-40A8-BF85-21CB00CDB44D}"/>
+  <xr:revisionPtr revIDLastSave="252" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ECE0D39-3581-4289-9AC0-EF9515F7DE2F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
@@ -25,6 +25,9 @@
     <sheet name="13-10" sheetId="10" r:id="rId10"/>
     <sheet name="14-10" sheetId="11" r:id="rId11"/>
     <sheet name="15-10" sheetId="12" r:id="rId12"/>
+    <sheet name="18-10" sheetId="13" r:id="rId13"/>
+    <sheet name="19-10" sheetId="15" r:id="rId14"/>
+    <sheet name="20-10" sheetId="16" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="286">
   <si>
     <t>Date</t>
   </si>
@@ -792,6 +795,123 @@
   </si>
   <si>
     <t>0182ICS0041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+  </si>
+  <si>
+    <t>000068-515-31</t>
+  </si>
+  <si>
+    <t>00133-515-31</t>
+  </si>
+  <si>
+    <t>00385-516-31</t>
+  </si>
+  <si>
+    <t>00701-509-31</t>
+  </si>
+  <si>
+    <t>00067-515-31</t>
+  </si>
+  <si>
+    <t>00108-515-31</t>
+  </si>
+  <si>
+    <t>00259-518-31</t>
+  </si>
+  <si>
+    <t>CMAU220385 /0</t>
+  </si>
+  <si>
+    <t>1730449</t>
+  </si>
+  <si>
+    <t>CMAU455459 /8</t>
+  </si>
+  <si>
+    <t>1730443</t>
+  </si>
+  <si>
+    <t>CMAU480173 /8</t>
+  </si>
+  <si>
+    <t>1730445</t>
+  </si>
+  <si>
+    <t>CMAU573921 /4</t>
+  </si>
+  <si>
+    <t>1730441</t>
+  </si>
+  <si>
+    <t>CMAU786292 /7</t>
+  </si>
+  <si>
+    <t>1730447</t>
+  </si>
+  <si>
+    <t>TCNU415361 /5</t>
+  </si>
+  <si>
+    <t>1730400</t>
+  </si>
+  <si>
+    <t>00311-515-31</t>
+  </si>
+  <si>
+    <t>00089-516-31</t>
+  </si>
+  <si>
+    <t>00177-525-31</t>
+  </si>
+  <si>
+    <t>00035-524-31</t>
+  </si>
+  <si>
+    <t>00005-517-31</t>
+  </si>
+  <si>
+    <t>000042-524-31</t>
+  </si>
+  <si>
+    <t>CAIU6645586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24H1702427 </t>
+  </si>
+  <si>
+    <t>00782ICS0012</t>
+  </si>
+  <si>
+    <t>TEMU359990 /0</t>
+  </si>
+  <si>
+    <t>FX46306546</t>
+  </si>
+  <si>
+    <t>00068-515-31</t>
+  </si>
+  <si>
+    <t>01447-590-31</t>
+  </si>
+  <si>
+    <t>02067-586-31</t>
+  </si>
+  <si>
+    <t>02119-587-31</t>
+  </si>
+  <si>
+    <t>02233-585-31</t>
+  </si>
+  <si>
+    <t>00154-517-31</t>
+  </si>
+  <si>
+    <t>MSDUI612394 /9</t>
+  </si>
+  <si>
+    <t>00154-517-32</t>
   </si>
 </sst>
 </file>
@@ -1511,6 +1631,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D077A503-8795-44BA-80A9-941A9CAC4D3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D31F7092-7058-4FC4-9C1E-C6065A7B9B44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="561975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88148696-BF96-4DFD-988D-6F715650F9E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="2000250" cy="581025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1951,6 +2236,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2518,33 +2807,66 @@
       </c>
       <c r="C12" s="3">
         <f>'15-10'!H2</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D12" s="4">
         <f>B12+C12</f>
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
+      <c r="A13" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B13" s="3">
+        <f>'18-10'!H1</f>
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
+        <f>'18-10'!H2</f>
+        <v>7</v>
+      </c>
+      <c r="D13" s="4">
+        <f>B13+C13</f>
+        <v>8</v>
+      </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B14" s="3">
+        <f>'19-10'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="3">
+        <f>'19-10'!H2</f>
+        <v>12</v>
+      </c>
+      <c r="D14" s="4">
+        <f>B14+C14</f>
+        <v>12</v>
+      </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
+      <c r="A15" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B15" s="3">
+        <f>'20-10'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <f>'20-10'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <f>B15+C15</f>
+        <v>0</v>
+      </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -2609,15 +2931,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D19)</f>
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3756,7 +4078,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8E4176-44D6-4CE5-8273-4AB7EA8EE430}">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
@@ -3774,7 +4096,7 @@
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="H1" s="8">
-        <f>COUNTIF(C8:C19,"&lt;&gt;")</f>
+        <f>COUNTIF(C8:C12,"&lt;&gt;")</f>
         <v>4</v>
       </c>
       <c r="I1" s="9" t="s">
@@ -3784,21 +4106,21 @@
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="F2" s="8">
-        <f>COUNTIFS(B26:B30,"&lt;&gt;",C26:C30,"VH")</f>
+        <f>COUNTIFS(B18:B22,"&lt;&gt;",C18:C22,"VH")</f>
         <v>0</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8">
-        <f>COUNTA(C26:C30)-F2</f>
-        <v>0</v>
+        <f>COUNTA(C18:C31)-F2</f>
+        <v>14</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="10">
-        <f>COUNTIF(E26:E30,"VIDE")</f>
+        <f>COUNTIF(E18:E22,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
@@ -3823,7 +4145,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="12">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3946,332 +4268,2255 @@
       <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
+      <c r="A13" s="6"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>1</v>
+      </c>
+      <c r="B18" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>2</v>
+      </c>
+      <c r="B19" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28">
+        <v>3</v>
+      </c>
+      <c r="B20" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="D20" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="28">
+        <v>5</v>
+      </c>
+      <c r="B22" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="B23" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="20"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="28">
+      <c r="B24" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="B25" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" s="26">
+        <v>3728</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
         <v>9</v>
-      </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
-        <v>11</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
-        <v>12</v>
-      </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="20"/>
-    </row>
-    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="28">
-        <v>13</v>
-      </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="20"/>
-    </row>
-    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="20"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
-        <v>1</v>
       </c>
       <c r="B26" s="19">
         <v>15102026</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
+      <c r="C26" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
-        <v>2</v>
-      </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="28"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
+        <v>10</v>
+      </c>
+      <c r="B27" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
-        <v>3</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="29"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
+        <v>11</v>
+      </c>
+      <c r="B28" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="28">
-        <v>4</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="29"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="B29" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
-        <v>5</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="29"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
+        <v>13</v>
+      </c>
+      <c r="B30" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="37"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="37"/>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="11" t="s">
+      <c r="A31" s="28">
+        <v>14</v>
+      </c>
+      <c r="B31" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="49"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B35" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C35" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D35" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E35" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F35" s="16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
-        <v>1</v>
-      </c>
-      <c r="B35" s="19">
-        <v>15102026</v>
-      </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
-        <v>2</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" s="31">
+        <v>3541</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" s="31">
+        <v>3542</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
         <v>3</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="28">
-        <v>4</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
+      <c r="B38" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" s="31">
+        <v>3543</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
-        <v>5</v>
-      </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
+        <v>4</v>
+      </c>
+      <c r="B39" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E39" s="31">
+        <v>3544</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="28">
+        <v>5</v>
+      </c>
+      <c r="B40" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="E40" s="31">
+        <v>3545</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
         <v>6</v>
       </c>
-      <c r="B40" s="59"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
+      <c r="B41" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="E41" s="31">
+        <v>3546</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="21" t="s">
+        <v>247</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F22" xr:uid="{D2398EA4-793A-4429-A19B-C4C1350F4CAE}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F36:F41 F18:F32 F8:F14" xr:uid="{D2398EA4-793A-4429-A19B-C4C1350F4CAE}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35:F39" xr:uid="{37301691-48F1-475D-BF15-1DEF68A23EB3}">
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0933031-B776-4E80-9AD3-EE516EF52D54}">
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C12,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B18:B22,"&lt;&gt;",C18:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C18:C31)-F2</f>
+        <v>7</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E18:E22,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" s="19">
+        <v>18102026</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="F8" s="24">
+        <v>20</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="46"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="46"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="46"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>1</v>
+      </c>
+      <c r="B18" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>2</v>
+      </c>
+      <c r="B19" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28">
+        <v>3</v>
+      </c>
+      <c r="B20" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="28">
+        <v>5</v>
+      </c>
+      <c r="B22" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="28">
+        <v>6</v>
+      </c>
+      <c r="B23" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
+        <v>7</v>
+      </c>
+      <c r="B24" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
+        <v>8</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="24"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>9</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="24"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>10</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="24"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>11</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="24"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>12</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="24"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>13</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>14</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="49"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="E36" s="31">
+        <v>3726</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="24"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>3</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>4</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>5</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>6</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F36:F41 F8:F14 F18:F32" xr:uid="{EFB631C9-122C-4158-8EA4-A02C82A5D1D3}">
       <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F5A9943-631D-4BCB-93ED-D5E0BD151C6D}">
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C12,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B18:B26,"&lt;&gt;",C18:C26,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C18:C30)-F2</f>
+        <v>12</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E18:E22,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="46"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="46"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="46"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>1</v>
+      </c>
+      <c r="B18" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>2</v>
+      </c>
+      <c r="B19" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28">
+        <v>3</v>
+      </c>
+      <c r="B20" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D21" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="28">
+        <v>5</v>
+      </c>
+      <c r="B22" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="D22" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="28">
+        <v>6</v>
+      </c>
+      <c r="B23" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
+        <v>7</v>
+      </c>
+      <c r="B24" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
+        <v>8</v>
+      </c>
+      <c r="B25" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="D25" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>9</v>
+      </c>
+      <c r="B26" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="D26" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>10</v>
+      </c>
+      <c r="B27" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" s="25">
+        <v>3727</v>
+      </c>
+      <c r="F27" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>11</v>
+      </c>
+      <c r="B28" s="19">
+        <v>19102026</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="25">
+        <v>3675</v>
+      </c>
+      <c r="F28" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>12</v>
+      </c>
+      <c r="B29" s="19">
+        <v>19102027</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="D29" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>13</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>14</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="49"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="31">
+        <v>3547</v>
+      </c>
+      <c r="F36" s="24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="24"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>3</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>4</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>5</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>6</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F36:F41 F8:F14 F18:F32" xr:uid="{7C84209B-4F35-43F1-BBBF-CBE7F2EF4D2A}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC71357C-A491-4F93-8861-224F3FE68F88}">
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C12,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B18:B22,"&lt;&gt;",C18:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C18:C31)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E18:E22,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="46"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="46"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="46"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>1</v>
+      </c>
+      <c r="B18" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>2</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="28"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28">
+        <v>3</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="28"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="28"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="28">
+        <v>5</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="28"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="28">
+        <v>6</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="28"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
+        <v>7</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
+        <v>8</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="24"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>9</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="24"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>10</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="24"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>11</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="24"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>12</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="24"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>13</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>14</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="49"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>15102026</v>
+      </c>
+      <c r="C36" s="26"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="24"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="24"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>3</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>4</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>5</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>6</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F36:F41 F8:F14 F18:F32" xr:uid="{D02264BE-9279-4926-AB01-DBCE0AE95BFC}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0AB0B5A2ED962CAE/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="252" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ECE0D39-3581-4289-9AC0-EF9515F7DE2F}"/>
+  <xr:revisionPtr revIDLastSave="392" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66BCC985-529D-4253-98CB-29621BF512AF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
@@ -28,6 +28,8 @@
     <sheet name="18-10" sheetId="13" r:id="rId13"/>
     <sheet name="19-10" sheetId="15" r:id="rId14"/>
     <sheet name="20-10" sheetId="16" r:id="rId15"/>
+    <sheet name="21-10" sheetId="17" r:id="rId16"/>
+    <sheet name="22-10" sheetId="18" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="314">
   <si>
     <t>Date</t>
   </si>
@@ -912,6 +914,90 @@
   </si>
   <si>
     <t>00154-517-32</t>
+  </si>
+  <si>
+    <t>001766-588-31</t>
+  </si>
+  <si>
+    <t>CMAU789256 /2</t>
+  </si>
+  <si>
+    <t>FSCU873148 /5</t>
+  </si>
+  <si>
+    <t>BMOU5526704</t>
+  </si>
+  <si>
+    <t>FX44773324</t>
+  </si>
+  <si>
+    <t>MSDU8628098</t>
+  </si>
+  <si>
+    <t>FX44780613</t>
+  </si>
+  <si>
+    <t>MSGU5164029</t>
+  </si>
+  <si>
+    <t>FX44780619</t>
+  </si>
+  <si>
+    <t>MSMU7207085</t>
+  </si>
+  <si>
+    <t>FX44780615</t>
+  </si>
+  <si>
+    <t>MSMU5339483</t>
+  </si>
+  <si>
+    <t>FX44692847</t>
+  </si>
+  <si>
+    <t>MSMU7636900</t>
+  </si>
+  <si>
+    <t>FX44796116</t>
+  </si>
+  <si>
+    <t>MSMU8206479</t>
+  </si>
+  <si>
+    <t>FX44692869</t>
+  </si>
+  <si>
+    <t>MSNU9865258</t>
+  </si>
+  <si>
+    <t>FX44796073</t>
+  </si>
+  <si>
+    <t>TGBU5881195</t>
+  </si>
+  <si>
+    <t>FX35719396</t>
+  </si>
+  <si>
+    <t>TLLU7904393</t>
+  </si>
+  <si>
+    <t>FX44692868</t>
+  </si>
+  <si>
+    <t>0184ICS0132</t>
+  </si>
+  <si>
+    <t>0184ICS0184</t>
+  </si>
+  <si>
+    <t>002255-585-31</t>
+  </si>
+  <si>
+    <t>00359-515-31</t>
+  </si>
+  <si>
+    <t>02255-585-31</t>
   </si>
 </sst>
 </file>
@@ -922,7 +1008,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1046,6 +1132,20 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1235,7 +1335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1448,6 +1548,36 @@
     </xf>
     <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1753,8 +1883,8 @@
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>828675</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1784,7 +1914,117 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="76200" y="0"/>
-          <a:ext cx="2000250" cy="581025"/>
+          <a:ext cx="2000250" cy="485775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B0F92FA-5770-45C6-B134-3AF7A870DC68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="1"/>
+          <a:ext cx="2000250" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE0548A1-0FA6-4D43-92AA-36C59568FD83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="1"/>
+          <a:ext cx="2000250" cy="495300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2738,7 +2978,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="4">
-        <f>B8+C8</f>
+        <f t="shared" ref="D8:D15" si="1">B8+C8</f>
         <v>19</v>
       </c>
       <c r="F8" s="3"/>
@@ -2756,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <f>B9+C9</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F9" s="3"/>
@@ -2774,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>B10+C10</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="F10" s="3"/>
@@ -2792,7 +3032,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="4">
-        <f>B11+C11</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="F11" s="3"/>
@@ -2810,7 +3050,7 @@
         <v>14</v>
       </c>
       <c r="D12" s="4">
-        <f>B12+C12</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="F12" s="3"/>
@@ -2828,7 +3068,7 @@
         <v>7</v>
       </c>
       <c r="D13" s="4">
-        <f>B13+C13</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="F13" s="3"/>
@@ -2846,7 +3086,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="4">
-        <f>B14+C14</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="F14" s="3"/>
@@ -2861,33 +3101,66 @@
       </c>
       <c r="C15" s="3">
         <f>'20-10'!H2</f>
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B16" s="3">
+        <f>'21-10'!H1</f>
+        <v>10</v>
+      </c>
+      <c r="C16" s="3">
+        <f>'21-10'!H2</f>
+        <v>4</v>
+      </c>
+      <c r="D16" s="4">
+        <f t="shared" ref="D16" si="2">B16+C16</f>
+        <v>14</v>
+      </c>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B17" s="3">
+        <f>'22-10'!H1</f>
         <v>0</v>
       </c>
-      <c r="D15" s="4">
-        <f>B15+C15</f>
+      <c r="C17" s="3">
+        <f>'22-10'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D17" s="4">
+        <f t="shared" ref="D17" si="3">B17+C17</f>
+        <v>2</v>
+      </c>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B18" s="3">
+        <f>'22-10'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="C18" s="3">
+        <f>'22-10'!H3</f>
         <v>0</v>
       </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <f t="shared" ref="D18" si="4">B18+C18</f>
+        <v>2</v>
+      </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -2931,15 +3204,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D24" s="5">
-        <f>SUM(D2:D19)</f>
-        <v>110</v>
+        <f>SUM(D2:D23)</f>
+        <v>129</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -5958,20 +6231,36 @@
         <v>2</v>
       </c>
       <c r="B37" s="19"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="24"/>
+      <c r="C37" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D37" s="25">
+        <v>3703</v>
+      </c>
+      <c r="E37" s="31">
+        <v>3721</v>
+      </c>
+      <c r="F37" s="24">
+        <v>40</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <v>3</v>
       </c>
       <c r="B38" s="19"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="24"/>
+      <c r="C38" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="D38" s="25">
+        <v>3701</v>
+      </c>
+      <c r="E38" s="31">
+        <v>3722</v>
+      </c>
+      <c r="F38" s="24">
+        <v>40</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
@@ -6063,7 +6352,7 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C18:C31)-F2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
@@ -6233,12 +6522,20 @@
         <v>1</v>
       </c>
       <c r="B18" s="19">
-        <v>15102026</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
+        <v>20102026</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="E18" s="28">
+        <v>3726</v>
+      </c>
+      <c r="F18" s="28">
+        <v>20</v>
+      </c>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="28">
@@ -6246,8 +6543,8 @@
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="29"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="25"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="31"/>
       <c r="F19" s="28"/>
       <c r="I19" s="33"/>
       <c r="J19" s="33"/>
@@ -6447,22 +6744,40 @@
         <v>1</v>
       </c>
       <c r="B36" s="19">
-        <v>15102026</v>
-      </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="24"/>
+        <v>20102026</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D36" s="31">
+        <v>3721</v>
+      </c>
+      <c r="E36" s="31">
+        <v>3548</v>
+      </c>
+      <c r="F36" s="24">
+        <v>40</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
         <v>2</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="24"/>
+      <c r="B37" s="19">
+        <v>20102026</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="D37" s="31">
+        <v>3722</v>
+      </c>
+      <c r="E37" s="31">
+        <v>3549</v>
+      </c>
+      <c r="F37" s="24">
+        <v>40</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
@@ -6515,6 +6830,1218 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F36:F41 F8:F14 F18:F32" xr:uid="{D02264BE-9279-4926-AB01-DBCE0AE95BFC}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF50D31A-92A1-4B5B-951E-69EBEE09D618}">
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C18,"&lt;&gt;")</f>
+        <v>10</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B24:B28,"&lt;&gt;",C24:C28,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C24:C33)-F2</f>
+        <v>4</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E24:E28,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="74" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>289</v>
+      </c>
+      <c r="E8" s="75" t="s">
+        <v>290</v>
+      </c>
+      <c r="F8" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="74"/>
+      <c r="C9" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D9" s="77" t="s">
+        <v>291</v>
+      </c>
+      <c r="E9" s="76" t="s">
+        <v>292</v>
+      </c>
+      <c r="F9" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="74"/>
+      <c r="C10" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D10" s="76" t="s">
+        <v>293</v>
+      </c>
+      <c r="E10" s="76" t="s">
+        <v>294</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="74"/>
+      <c r="C11" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D11" s="76" t="s">
+        <v>295</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>296</v>
+      </c>
+      <c r="F11" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>310</v>
+      </c>
+      <c r="C12" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D12" s="76" t="s">
+        <v>297</v>
+      </c>
+      <c r="E12" s="79" t="s">
+        <v>298</v>
+      </c>
+      <c r="F12" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="78"/>
+      <c r="C13" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D13" s="76" t="s">
+        <v>299</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>300</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="78"/>
+      <c r="C14" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D14" s="76" t="s">
+        <v>301</v>
+      </c>
+      <c r="E14" s="79" t="s">
+        <v>302</v>
+      </c>
+      <c r="F14" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="78"/>
+      <c r="C15" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D15" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="E15" s="79" t="s">
+        <v>304</v>
+      </c>
+      <c r="F15" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="78"/>
+      <c r="C16" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D16" s="80" t="s">
+        <v>305</v>
+      </c>
+      <c r="E16" s="79" t="s">
+        <v>306</v>
+      </c>
+      <c r="F16" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>10</v>
+      </c>
+      <c r="B17" s="78"/>
+      <c r="C17" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="D17" s="80" t="s">
+        <v>307</v>
+      </c>
+      <c r="E17" s="79" t="s">
+        <v>308</v>
+      </c>
+      <c r="F17" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>11</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
+        <v>1</v>
+      </c>
+      <c r="B24" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" s="28">
+        <v>3671</v>
+      </c>
+      <c r="F24" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
+        <v>2</v>
+      </c>
+      <c r="B25" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="28">
+        <v>3629</v>
+      </c>
+      <c r="F25" s="28">
+        <v>40</v>
+      </c>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>3</v>
+      </c>
+      <c r="B26" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="D27" s="73" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="25">
+        <v>3630</v>
+      </c>
+      <c r="F27" s="28">
+        <v>40</v>
+      </c>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>5</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="28"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>6</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="28"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>7</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>8</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28">
+        <v>9</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="24"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28">
+        <v>10</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="24"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="49"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>1</v>
+      </c>
+      <c r="B38" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="31">
+        <v>3725</v>
+      </c>
+      <c r="F38" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>2</v>
+      </c>
+      <c r="B39" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="31">
+        <v>3550</v>
+      </c>
+      <c r="F39" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>3</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>4</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="28">
+        <v>5</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="24"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="28">
+        <v>6</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="24"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B12:B17"/>
+  </mergeCells>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F43 F8:F20 F24:F34" xr:uid="{062F37CD-A779-40C2-A34B-D2174CE6D1F3}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57F27C90-9A53-421F-A4AA-EB52E45F57C1}">
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C18,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B24:B28,"&lt;&gt;",C24:C28,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C24:C33)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E24:E28,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="81"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="81"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="81"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="81"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="82"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="82"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="82"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="82"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="82"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>10</v>
+      </c>
+      <c r="B17" s="82"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>11</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
+        <v>1</v>
+      </c>
+      <c r="B24" s="19">
+        <v>22102026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="F24" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
+        <v>2</v>
+      </c>
+      <c r="B25" s="19">
+        <v>22102026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="F25" s="28">
+        <v>45</v>
+      </c>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>3</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="28"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>5</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="28"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>6</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="28"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>7</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>8</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28">
+        <v>9</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="24"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28">
+        <v>10</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="24"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="49"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>1</v>
+      </c>
+      <c r="B38" s="19">
+        <v>21102026</v>
+      </c>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>2</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>3</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>4</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="28">
+        <v>5</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="24"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="28">
+        <v>6</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="24"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F43 F8:F20 F24:F34" xr:uid="{D28D13AC-8119-47AF-A67D-07D66B22E1FA}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0AB0B5A2ED962CAE/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="392" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66BCC985-529D-4253-98CB-29621BF512AF}"/>
+  <xr:revisionPtr revIDLastSave="565" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1629ED0F-7BEC-49C1-B513-30FC7CC9E852}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" firstSheet="6" activeTab="19" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,12 @@
     <sheet name="20-10" sheetId="16" r:id="rId15"/>
     <sheet name="21-10" sheetId="17" r:id="rId16"/>
     <sheet name="22-10" sheetId="18" r:id="rId17"/>
+    <sheet name="25-10" sheetId="19" r:id="rId18"/>
+    <sheet name="26-10" sheetId="20" r:id="rId19"/>
+    <sheet name="27-10" sheetId="21" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -55,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="368">
   <si>
     <t>Date</t>
   </si>
@@ -998,6 +1002,168 @@
   </si>
   <si>
     <t>02255-585-31</t>
+  </si>
+  <si>
+    <t>0161-511-31</t>
+  </si>
+  <si>
+    <t>00098-509-31</t>
+  </si>
+  <si>
+    <t>00068-516-31</t>
+  </si>
+  <si>
+    <t>CMAU255168 /7</t>
+  </si>
+  <si>
+    <t>ECMU298872 /5</t>
+  </si>
+  <si>
+    <t>FCIU415741 /0</t>
+  </si>
+  <si>
+    <t>00044-595-31</t>
+  </si>
+  <si>
+    <t>00089-515-31</t>
+  </si>
+  <si>
+    <t>000372-512-31</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>00050-514-31</t>
+  </si>
+  <si>
+    <t>00271-503-31</t>
+  </si>
+  <si>
+    <t>005003-525-02</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>MSMU932960 /5</t>
+  </si>
+  <si>
+    <t>FJ28511677</t>
+  </si>
+  <si>
+    <t>BNSU4503130</t>
+  </si>
+  <si>
+    <t>LB0218323</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>CLXU4502637</t>
+  </si>
+  <si>
+    <t>LB0218324</t>
+  </si>
+  <si>
+    <t>CLXU4503799</t>
+  </si>
+  <si>
+    <t>LB0218325</t>
+  </si>
+  <si>
+    <t>CLXU4505512</t>
+  </si>
+  <si>
+    <t>LB0232412</t>
+  </si>
+  <si>
+    <t>CLXU4511599</t>
+  </si>
+  <si>
+    <t>LB0218321</t>
+  </si>
+  <si>
+    <t>TCLU4809882</t>
+  </si>
+  <si>
+    <t>LB0218322</t>
+  </si>
+  <si>
+    <t>OOCU0979651</t>
+  </si>
+  <si>
+    <t>33622887</t>
+  </si>
+  <si>
+    <t>CMAU0567236</t>
+  </si>
+  <si>
+    <t>M1583073</t>
+  </si>
+  <si>
+    <t>0042ICS0003</t>
+  </si>
+  <si>
+    <t>0196ICS0007</t>
+  </si>
+  <si>
+    <t>0933ICS0018</t>
+  </si>
+  <si>
+    <t>CMAU238193 /4</t>
+  </si>
+  <si>
+    <t>02367-586-31</t>
+  </si>
+  <si>
+    <t>000693-509-31</t>
+  </si>
+  <si>
+    <t>FCIU6329246</t>
+  </si>
+  <si>
+    <t>AG570427</t>
+  </si>
+  <si>
+    <t>TCLU3255908</t>
+  </si>
+  <si>
+    <t>AG570449</t>
+  </si>
+  <si>
+    <t>TEMU2622478</t>
+  </si>
+  <si>
+    <t>AG570450</t>
+  </si>
+  <si>
+    <t>0297ICS0006</t>
+  </si>
+  <si>
+    <t>CAIU986982 /5</t>
+  </si>
+  <si>
+    <t>FX45999499</t>
+  </si>
+  <si>
+    <t>MSDU652953 /7</t>
+  </si>
+  <si>
+    <t>FX45999474</t>
+  </si>
+  <si>
+    <t>MSNU593133 /0</t>
+  </si>
+  <si>
+    <t>FX46020281</t>
+  </si>
+  <si>
+    <t>00426-504-31</t>
+  </si>
+  <si>
+    <t>02177-588-31</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1376,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1331,11 +1497,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1525,6 +1704,33 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1549,35 +1755,14 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2025,6 +2210,171 @@
         <a:xfrm>
           <a:off x="76200" y="1"/>
           <a:ext cx="2000250" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4606B2F6-5F9A-46FC-9DC4-5F36CDD15A14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="1"/>
+          <a:ext cx="2000250" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F42E6EAD-7C42-4C5E-A0A5-D69EBE2259C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="1"/>
+          <a:ext cx="2000250" cy="533400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B2BC239-AB99-44EB-B689-F6F48DB11A0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="1"/>
+          <a:ext cx="2000250" cy="514350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3137,37 +3487,48 @@
       </c>
       <c r="C17" s="3">
         <f>'22-10'!H2</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" ref="D17" si="3">B17+C17</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="B18" s="3">
-        <f>'22-10'!H2</f>
-        <v>2</v>
+        <f>'25-10'!H1</f>
+        <v>0</v>
       </c>
       <c r="C18" s="3">
-        <f>'22-10'!H3</f>
-        <v>0</v>
+        <f>'25-10'!H2</f>
+        <v>6</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" ref="D18" si="4">B18+C18</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
+      <c r="A19" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B19" s="3">
+        <f>'26-10'!H1</f>
+        <v>8</v>
+      </c>
+      <c r="C19" s="3">
+        <f>'26-10'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <f t="shared" ref="D19" si="5">B19+C19</f>
+        <v>8</v>
+      </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3204,15 +3565,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D23)</f>
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3272,16 +3633,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3866,16 +4227,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4398,16 +4759,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5134,16 +5495,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5720,16 +6081,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6363,16 +6724,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6889,16 +7250,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6940,19 +7301,19 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="82" t="s">
         <v>309</v>
       </c>
       <c r="C8" s="19">
         <v>21102026</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="66" t="s">
         <v>289</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="66" t="s">
         <v>290</v>
       </c>
-      <c r="F8" s="76" t="s">
+      <c r="F8" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="20"/>
@@ -6961,17 +7322,17 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="74"/>
+      <c r="B9" s="82"/>
       <c r="C9" s="19">
         <v>21102026</v>
       </c>
-      <c r="D9" s="77" t="s">
+      <c r="D9" s="68" t="s">
         <v>291</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="67" t="s">
         <v>292</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="20"/>
@@ -6980,17 +7341,17 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="74"/>
+      <c r="B10" s="82"/>
       <c r="C10" s="19">
         <v>21102026</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="67" t="s">
         <v>293</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="20"/>
@@ -6999,17 +7360,17 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="74"/>
+      <c r="B11" s="82"/>
       <c r="C11" s="19">
         <v>21102026</v>
       </c>
-      <c r="D11" s="76" t="s">
+      <c r="D11" s="67" t="s">
         <v>295</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="67" t="s">
         <v>296</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="20"/>
@@ -7018,19 +7379,19 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="83" t="s">
         <v>310</v>
       </c>
       <c r="C12" s="19">
         <v>21102026</v>
       </c>
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="67" t="s">
         <v>297</v>
       </c>
-      <c r="E12" s="79" t="s">
+      <c r="E12" s="69" t="s">
         <v>298</v>
       </c>
-      <c r="F12" s="76" t="s">
+      <c r="F12" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G12" s="20"/>
@@ -7039,17 +7400,17 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="78"/>
+      <c r="B13" s="83"/>
       <c r="C13" s="19">
         <v>21102026</v>
       </c>
-      <c r="D13" s="76" t="s">
+      <c r="D13" s="67" t="s">
         <v>299</v>
       </c>
-      <c r="E13" s="79" t="s">
+      <c r="E13" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="F13" s="76" t="s">
+      <c r="F13" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G13" s="20"/>
@@ -7058,17 +7419,17 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="78"/>
+      <c r="B14" s="83"/>
       <c r="C14" s="19">
         <v>21102026</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="E14" s="79" t="s">
+      <c r="E14" s="69" t="s">
         <v>302</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G14" s="20"/>
@@ -7077,17 +7438,17 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="78"/>
+      <c r="B15" s="83"/>
       <c r="C15" s="19">
         <v>21102026</v>
       </c>
-      <c r="D15" s="80" t="s">
+      <c r="D15" s="70" t="s">
         <v>303</v>
       </c>
-      <c r="E15" s="79" t="s">
+      <c r="E15" s="69" t="s">
         <v>304</v>
       </c>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G15" s="20"/>
@@ -7096,17 +7457,17 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="78"/>
+      <c r="B16" s="83"/>
       <c r="C16" s="19">
         <v>21102026</v>
       </c>
-      <c r="D16" s="80" t="s">
+      <c r="D16" s="70" t="s">
         <v>305</v>
       </c>
-      <c r="E16" s="79" t="s">
+      <c r="E16" s="69" t="s">
         <v>306</v>
       </c>
-      <c r="F16" s="76" t="s">
+      <c r="F16" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G16" s="20"/>
@@ -7115,17 +7476,17 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="78"/>
+      <c r="B17" s="83"/>
       <c r="C17" s="19">
         <v>21102026</v>
       </c>
-      <c r="D17" s="80" t="s">
+      <c r="D17" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="E17" s="79" t="s">
+      <c r="E17" s="69" t="s">
         <v>308</v>
       </c>
-      <c r="F17" s="76" t="s">
+      <c r="F17" s="67" t="s">
         <v>38</v>
       </c>
       <c r="G17" s="20"/>
@@ -7273,7 +7634,7 @@
       <c r="C27" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="D27" s="73" t="s">
+      <c r="D27" s="65" t="s">
         <v>195</v>
       </c>
       <c r="E27" s="25">
@@ -7449,21 +7810,35 @@
       <c r="A40" s="28">
         <v>3</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="24"/>
+      <c r="B40" s="19">
+        <v>22102026</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D40" s="31">
+        <v>3548</v>
+      </c>
+      <c r="F40" s="24">
+        <v>40</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="28">
         <v>4</v>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="24"/>
+      <c r="B41" s="19">
+        <v>22102026</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="D41" s="31">
+        <v>3549</v>
+      </c>
+      <c r="F41" s="24">
+        <v>40</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="28">
@@ -7497,7 +7872,7 @@
     <mergeCell ref="B12:B17"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F43 F8:F20 F24:F34" xr:uid="{062F37CD-A779-40C2-A34B-D2174CE6D1F3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24:F34 F8:F20 F38:F43" xr:uid="{062F37CD-A779-40C2-A34B-D2174CE6D1F3}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7538,7 +7913,7 @@
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="F2" s="8">
-        <f>COUNTIFS(B24:B28,"&lt;&gt;",C24:C28,"VH")</f>
+        <f>COUNTIFS(B24:B39,"&lt;&gt;",C24:C39,"VH")</f>
         <v>0</v>
       </c>
       <c r="G2" s="9" t="s">
@@ -7546,27 +7921,27 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C24:C33)-F2</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="10">
-        <f>COUNTIF(E24:E28,"VIDE")</f>
+        <f>COUNTIF(E24:E39,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7608,110 +7983,110 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="81"/>
+      <c r="B8" s="71"/>
       <c r="C8" s="19"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
       <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="81"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="19"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
       <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="81"/>
+      <c r="B10" s="71"/>
       <c r="C10" s="19"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
       <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="81"/>
+      <c r="B11" s="71"/>
       <c r="C11" s="19"/>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
       <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="82"/>
+      <c r="B12" s="72"/>
       <c r="C12" s="19"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="76"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="67"/>
       <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="82"/>
+      <c r="B13" s="72"/>
       <c r="C13" s="19"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="76"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="67"/>
       <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="82"/>
+      <c r="B14" s="72"/>
       <c r="C14" s="19"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="76"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="67"/>
       <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="82"/>
+      <c r="B15" s="72"/>
       <c r="C15" s="19"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="76"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="67"/>
       <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="82"/>
+      <c r="B16" s="72"/>
       <c r="C16" s="19"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="76"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="67"/>
       <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="82"/>
+      <c r="B17" s="72"/>
       <c r="C17" s="19"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="76"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="67"/>
       <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -7826,11 +8201,21 @@
       <c r="A26" s="28">
         <v>3</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
+      <c r="B26" s="19">
+        <v>22102026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="31">
+        <v>3547</v>
+      </c>
+      <c r="F26" s="24">
+        <v>20</v>
+      </c>
       <c r="I26" s="33"/>
       <c r="J26" s="33"/>
       <c r="K26" s="33"/>
@@ -7841,11 +8226,21 @@
       <c r="A27" s="28">
         <v>4</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="28"/>
+      <c r="B27" s="19">
+        <v>22102027</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="31">
+        <v>3725</v>
+      </c>
+      <c r="F27" s="24">
+        <v>40</v>
+      </c>
       <c r="I27" s="33"/>
       <c r="J27" s="33"/>
       <c r="K27" s="33"/>
@@ -7856,11 +8251,21 @@
       <c r="A28" s="28">
         <v>5</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="28"/>
+      <c r="B28" s="19">
+        <v>22102028</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="31">
+        <v>3550</v>
+      </c>
+      <c r="F28" s="24">
+        <v>40</v>
+      </c>
       <c r="I28" s="33"/>
       <c r="J28" s="33"/>
       <c r="K28" s="33"/>
@@ -7973,12 +8378,10 @@
       <c r="A38" s="28">
         <v>1</v>
       </c>
-      <c r="B38" s="19">
-        <v>21102026</v>
-      </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="31"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="59"/>
       <c r="F38" s="24"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7987,8 +8390,8 @@
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="59"/>
       <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8040,14 +8443,1241 @@
   <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F43 F8:F20 F24:F34" xr:uid="{D28D13AC-8119-47AF-A67D-07D66B22E1FA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F20 F38:F43 F24:F34" xr:uid="{D28D13AC-8119-47AF-A67D-07D66B22E1FA}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C43BB8-91D3-476A-BAA8-83E749D3FC79}">
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C18,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B24:B39,"&lt;&gt;",C24:C39,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C24:C33)-F2</f>
+        <v>6</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E24:E39,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="71"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="71"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="71"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="71"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="72"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="72"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="72"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="72"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="72"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>10</v>
+      </c>
+      <c r="B17" s="72"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>11</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
+        <v>1</v>
+      </c>
+      <c r="B24" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="F24" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
+        <v>2</v>
+      </c>
+      <c r="B25" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="F25" s="28">
+        <v>20</v>
+      </c>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>3</v>
+      </c>
+      <c r="B26" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="F26" s="24">
+        <v>20</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="24">
+        <v>40</v>
+      </c>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>5</v>
+      </c>
+      <c r="B28" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="31">
+        <v>3628</v>
+      </c>
+      <c r="F28" s="24">
+        <v>40</v>
+      </c>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>6</v>
+      </c>
+      <c r="B29" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" s="26">
+        <v>3627</v>
+      </c>
+      <c r="F29" s="28">
+        <v>40</v>
+      </c>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>7</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>8</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28">
+        <v>9</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="24"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28">
+        <v>10</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="24"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="49"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>1</v>
+      </c>
+      <c r="B38" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C38" s="65" t="s">
+        <v>328</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="E38" s="31">
+        <v>3724</v>
+      </c>
+      <c r="F38" s="24">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>2</v>
+      </c>
+      <c r="B39" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>289</v>
+      </c>
+      <c r="D39" s="66" t="s">
+        <v>290</v>
+      </c>
+      <c r="E39" s="31">
+        <v>3597</v>
+      </c>
+      <c r="F39" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>3</v>
+      </c>
+      <c r="B40" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C40" s="68" t="s">
+        <v>291</v>
+      </c>
+      <c r="D40" s="67" t="s">
+        <v>292</v>
+      </c>
+      <c r="E40" s="31">
+        <v>3600</v>
+      </c>
+      <c r="F40" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>4</v>
+      </c>
+      <c r="B41" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>293</v>
+      </c>
+      <c r="D41" s="67" t="s">
+        <v>294</v>
+      </c>
+      <c r="E41" s="31">
+        <v>3599</v>
+      </c>
+      <c r="F41" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="28">
+        <v>5</v>
+      </c>
+      <c r="B42" s="19">
+        <v>25102026</v>
+      </c>
+      <c r="C42" s="67" t="s">
+        <v>295</v>
+      </c>
+      <c r="D42" s="67" t="s">
+        <v>296</v>
+      </c>
+      <c r="E42" s="31">
+        <v>3598</v>
+      </c>
+      <c r="F42" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="28">
+        <v>6</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="24"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F20 F38:F43 F24:F34" xr:uid="{949D1F3A-94F3-4C58-8A6A-12907B3F691E}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7C42FDF-CDDE-41AC-AB5A-A7970820F30F}">
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C18,"&lt;&gt;")</f>
+        <v>8</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B24:B39,"&lt;&gt;",C24:C39,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C24:C33)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E24:E39,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="19">
+        <v>26102026</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="66" t="s">
+        <v>331</v>
+      </c>
+      <c r="F8" s="67" t="s">
+        <v>332</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="82"/>
+      <c r="C9" s="19">
+        <v>26102026</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>334</v>
+      </c>
+      <c r="F9" s="67" t="s">
+        <v>332</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="82"/>
+      <c r="C10" s="19">
+        <v>26102026</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>335</v>
+      </c>
+      <c r="E10" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="F10" s="67" t="s">
+        <v>332</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="82"/>
+      <c r="C11" s="19">
+        <v>26102026</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="F11" s="67" t="s">
+        <v>332</v>
+      </c>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="82"/>
+      <c r="C12" s="19">
+        <v>26102026</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>339</v>
+      </c>
+      <c r="E12" s="69" t="s">
+        <v>340</v>
+      </c>
+      <c r="F12" s="67" t="s">
+        <v>332</v>
+      </c>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="82"/>
+      <c r="C13" s="19">
+        <v>26102026</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>341</v>
+      </c>
+      <c r="E13" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="F13" s="67" t="s">
+        <v>332</v>
+      </c>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="73" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="19">
+        <v>26102026</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="69" t="s">
+        <v>344</v>
+      </c>
+      <c r="F14" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="73" t="s">
+        <v>349</v>
+      </c>
+      <c r="C15" s="19">
+        <v>26102026</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>345</v>
+      </c>
+      <c r="E15" s="69" t="s">
+        <v>346</v>
+      </c>
+      <c r="F15" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="72"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>10</v>
+      </c>
+      <c r="B17" s="72"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>11</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
+        <v>1</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="28"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
+        <v>2</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="28"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>3</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="24"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="24"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>5</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="24"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>6</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="28"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>7</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>8</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28">
+        <v>9</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="24"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28">
+        <v>10</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="24"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="49"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>1</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>2</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>3</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>4</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="28">
+        <v>5</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="24"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="28">
+        <v>6</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="24"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:B13"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24:F34 F38:F43 F8:F20" xr:uid="{D8E49EE4-E37F-43EF-AE27-C6F95BCA22A0}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -8101,16 +9731,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8608,6 +10238,604 @@
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48D2CC8-9E86-4801-8F04-CBE9B8C2AB40}">
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C18,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B24:B37,"&lt;&gt;",C24:C37,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C24:C31)-F2</f>
+        <v>5</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E24:E37,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>1</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>353</v>
+      </c>
+      <c r="E8" s="66" t="s">
+        <v>354</v>
+      </c>
+      <c r="F8" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" s="82"/>
+      <c r="C9" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>355</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>356</v>
+      </c>
+      <c r="F9" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>3</v>
+      </c>
+      <c r="B10" s="82"/>
+      <c r="C10" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="E10" s="67" t="s">
+        <v>358</v>
+      </c>
+      <c r="F10" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>4</v>
+      </c>
+      <c r="B11" s="71"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>5</v>
+      </c>
+      <c r="B12" s="72"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>6</v>
+      </c>
+      <c r="B13" s="72"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>7</v>
+      </c>
+      <c r="B14" s="72"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>8</v>
+      </c>
+      <c r="B15" s="72"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>9</v>
+      </c>
+      <c r="B16" s="72"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>10</v>
+      </c>
+      <c r="B17" s="72"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>11</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="28">
+        <v>1</v>
+      </c>
+      <c r="B24" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="E24" s="24">
+        <v>3677</v>
+      </c>
+      <c r="F24" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28">
+        <v>2</v>
+      </c>
+      <c r="B25" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="E25" s="28">
+        <v>3678</v>
+      </c>
+      <c r="F25" s="28">
+        <v>20</v>
+      </c>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
+        <v>3</v>
+      </c>
+      <c r="B26" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="D27" s="66" t="s">
+        <v>289</v>
+      </c>
+      <c r="E27" s="31">
+        <v>3597</v>
+      </c>
+      <c r="F27" s="24">
+        <v>40</v>
+      </c>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="D28" s="67" t="s">
+        <v>295</v>
+      </c>
+      <c r="E28" s="31">
+        <v>3598</v>
+      </c>
+      <c r="F28" s="24">
+        <v>40</v>
+      </c>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="24"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
+        <v>10</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="49"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C36" s="84" t="s">
+        <v>360</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>361</v>
+      </c>
+      <c r="E36" s="31">
+        <v>3595</v>
+      </c>
+      <c r="F36" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C37" s="84" t="s">
+        <v>362</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>363</v>
+      </c>
+      <c r="E37" s="31">
+        <v>3596</v>
+      </c>
+      <c r="F37" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28">
+        <v>3</v>
+      </c>
+      <c r="B38" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C38" s="84" t="s">
+        <v>364</v>
+      </c>
+      <c r="D38" s="43" t="s">
+        <v>365</v>
+      </c>
+      <c r="E38" s="31">
+        <v>3594</v>
+      </c>
+      <c r="F38" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="28">
+        <v>4</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="28">
+        <v>5</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="28">
+        <v>6</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:B10"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F20 F36:F41 F24:F32" xr:uid="{5918CB6E-FE11-4CC1-8449-E715B81D557B}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8661,16 +10889,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9245,16 +11473,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9879,16 +12107,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9930,7 +12158,7 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="75" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -9951,7 +12179,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="67"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="19">
         <v>6102026</v>
       </c>
@@ -9970,7 +12198,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="67"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="19">
         <v>6102026</v>
       </c>
@@ -9989,7 +12217,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="67"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="19">
         <v>6102026</v>
       </c>
@@ -10008,7 +12236,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="67"/>
+      <c r="B12" s="76"/>
       <c r="C12" s="57"/>
       <c r="D12" s="51" t="s">
         <v>125</v>
@@ -10025,7 +12253,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="67"/>
+      <c r="B13" s="76"/>
       <c r="C13" s="57"/>
       <c r="D13" s="51" t="s">
         <v>123</v>
@@ -10042,7 +12270,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="67"/>
+      <c r="B14" s="76"/>
       <c r="C14" s="57"/>
       <c r="D14" s="51" t="s">
         <v>121</v>
@@ -10059,7 +12287,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="67"/>
+      <c r="B15" s="76"/>
       <c r="C15" s="19">
         <v>6102026</v>
       </c>
@@ -10078,7 +12306,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="67"/>
+      <c r="B16" s="76"/>
       <c r="C16" s="57"/>
       <c r="D16" s="56" t="s">
         <v>117</v>
@@ -10095,7 +12323,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="67"/>
+      <c r="B17" s="76"/>
       <c r="C17" s="19">
         <v>6102026</v>
       </c>
@@ -10114,7 +12342,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="67"/>
+      <c r="B18" s="76"/>
       <c r="C18" s="57"/>
       <c r="D18" s="51" t="s">
         <v>113</v>
@@ -10131,7 +12359,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="67"/>
+      <c r="B19" s="76"/>
       <c r="C19" s="19">
         <v>6102026</v>
       </c>
@@ -10150,7 +12378,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="67"/>
+      <c r="B20" s="76"/>
       <c r="C20" s="57"/>
       <c r="D20" s="51" t="s">
         <v>109</v>
@@ -10167,7 +12395,7 @@
       <c r="A21" s="17">
         <v>14</v>
       </c>
-      <c r="B21" s="67"/>
+      <c r="B21" s="76"/>
       <c r="C21" s="57"/>
       <c r="D21" s="51" t="s">
         <v>107</v>
@@ -10184,7 +12412,7 @@
       <c r="A22" s="17">
         <v>15</v>
       </c>
-      <c r="B22" s="67"/>
+      <c r="B22" s="76"/>
       <c r="C22" s="57"/>
       <c r="D22" s="51" t="s">
         <v>105</v>
@@ -10201,7 +12429,7 @@
       <c r="A23" s="17">
         <v>16</v>
       </c>
-      <c r="B23" s="67"/>
+      <c r="B23" s="76"/>
       <c r="C23" s="57"/>
       <c r="D23" s="56" t="s">
         <v>103</v>
@@ -10218,7 +12446,7 @@
       <c r="A24" s="17">
         <v>17</v>
       </c>
-      <c r="B24" s="67"/>
+      <c r="B24" s="76"/>
       <c r="C24" s="19">
         <v>6102026</v>
       </c>
@@ -10237,7 +12465,7 @@
       <c r="A25" s="17">
         <v>18</v>
       </c>
-      <c r="B25" s="67"/>
+      <c r="B25" s="76"/>
       <c r="C25" s="19">
         <v>6102026</v>
       </c>
@@ -10256,7 +12484,7 @@
       <c r="A26" s="17">
         <v>19</v>
       </c>
-      <c r="B26" s="67"/>
+      <c r="B26" s="76"/>
       <c r="C26" s="19">
         <v>6102026</v>
       </c>
@@ -10275,7 +12503,7 @@
       <c r="A27" s="17">
         <v>20</v>
       </c>
-      <c r="B27" s="67"/>
+      <c r="B27" s="76"/>
       <c r="C27" s="19">
         <v>6102026</v>
       </c>
@@ -10294,7 +12522,7 @@
       <c r="A28" s="17">
         <v>21</v>
       </c>
-      <c r="B28" s="67"/>
+      <c r="B28" s="76"/>
       <c r="C28" s="57"/>
       <c r="D28" s="56" t="s">
         <v>93</v>
@@ -10311,7 +12539,7 @@
       <c r="A29" s="17">
         <v>22</v>
       </c>
-      <c r="B29" s="67"/>
+      <c r="B29" s="76"/>
       <c r="C29" s="19">
         <v>6102026</v>
       </c>
@@ -10330,7 +12558,7 @@
       <c r="A30" s="17">
         <v>23</v>
       </c>
-      <c r="B30" s="67"/>
+      <c r="B30" s="76"/>
       <c r="C30" s="19">
         <v>6102026</v>
       </c>
@@ -10349,7 +12577,7 @@
       <c r="A31" s="17">
         <v>24</v>
       </c>
-      <c r="B31" s="68"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="19">
         <v>6102026</v>
       </c>
@@ -10586,16 +12814,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10637,7 +12865,7 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="78" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -10658,7 +12886,7 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="69"/>
+      <c r="B9" s="78"/>
       <c r="C9" s="19">
         <v>7102026</v>
       </c>
@@ -10677,7 +12905,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="69"/>
+      <c r="B10" s="78"/>
       <c r="C10" s="19">
         <v>7102026</v>
       </c>
@@ -10696,7 +12924,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="69"/>
+      <c r="B11" s="78"/>
       <c r="C11" s="19">
         <v>7102026</v>
       </c>
@@ -10715,7 +12943,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="69"/>
+      <c r="B12" s="78"/>
       <c r="C12" s="19">
         <v>7102026</v>
       </c>
@@ -10734,7 +12962,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="69"/>
+      <c r="B13" s="78"/>
       <c r="C13" s="19">
         <v>7102026</v>
       </c>
@@ -10753,7 +12981,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="69"/>
+      <c r="B14" s="78"/>
       <c r="C14" s="19">
         <v>7102026</v>
       </c>
@@ -10772,7 +13000,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="69"/>
+      <c r="B15" s="78"/>
       <c r="C15" s="19">
         <v>7102026</v>
       </c>
@@ -10791,7 +13019,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="69"/>
+      <c r="B16" s="78"/>
       <c r="C16" s="19">
         <v>7102026</v>
       </c>
@@ -10810,7 +13038,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="69"/>
+      <c r="B17" s="78"/>
       <c r="C17" s="19">
         <v>7102026</v>
       </c>
@@ -10829,7 +13057,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="78" t="s">
         <v>137</v>
       </c>
       <c r="C18" s="19">
@@ -10850,7 +13078,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="69"/>
+      <c r="B19" s="78"/>
       <c r="C19" s="19">
         <v>7102026</v>
       </c>
@@ -11162,16 +13390,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11692,16 +13920,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11785,7 +14013,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="79" t="s">
         <v>187</v>
       </c>
       <c r="C10" s="19">
@@ -11806,7 +14034,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="71"/>
+      <c r="B11" s="80"/>
       <c r="C11" s="19">
         <v>11102026</v>
       </c>
@@ -11825,7 +14053,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="71"/>
+      <c r="B12" s="80"/>
       <c r="C12" s="19">
         <v>11102026</v>
       </c>
@@ -11844,7 +14072,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="71"/>
+      <c r="B13" s="80"/>
       <c r="C13" s="19">
         <v>11102026</v>
       </c>
@@ -11863,7 +14091,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="71"/>
+      <c r="B14" s="80"/>
       <c r="C14" s="19">
         <v>11102026</v>
       </c>
@@ -11882,7 +14110,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="72"/>
+      <c r="B15" s="81"/>
       <c r="C15" s="19">
         <v>11102026</v>
       </c>
@@ -11901,7 +14129,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="70" t="s">
+      <c r="B16" s="79" t="s">
         <v>188</v>
       </c>
       <c r="C16" s="19">
@@ -11922,7 +14150,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="71"/>
+      <c r="B17" s="80"/>
       <c r="C17" s="19">
         <v>11102026</v>
       </c>
@@ -11941,7 +14169,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="71"/>
+      <c r="B18" s="80"/>
       <c r="C18" s="19">
         <v>11102026</v>
       </c>
@@ -11960,7 +14188,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="71"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="19">
         <v>11102026</v>
       </c>
@@ -11979,7 +14207,7 @@
       <c r="A20" s="28">
         <v>13</v>
       </c>
-      <c r="B20" s="71"/>
+      <c r="B20" s="80"/>
       <c r="C20" s="19">
         <v>11102026</v>
       </c>
@@ -11998,7 +14226,7 @@
       <c r="A21" s="28">
         <v>14</v>
       </c>
-      <c r="B21" s="72"/>
+      <c r="B21" s="81"/>
       <c r="C21" s="19">
         <v>11102026</v>
       </c>
@@ -12429,16 +14657,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>

--- a/Fiche de mouvement _10-2026.xlsx
+++ b/Fiche de mouvement _10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0AB0B5A2ED962CAE/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="565" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1629ED0F-7BEC-49C1-B513-30FC7CC9E852}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="8_{0FD41444-73C9-4658-8652-2E2F595BA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC71D5A0-FA05-4A4C-B299-D653DF6FFAED}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" firstSheet="6" activeTab="19" xr2:uid="{A18A3B28-6AD6-4212-865A-5BA1C5CD781C}"/>
   </bookViews>
@@ -35,7 +35,6 @@
     <sheet name="27-10" sheetId="21" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -59,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="379">
   <si>
     <t>Date</t>
   </si>
@@ -1164,6 +1163,39 @@
   </si>
   <si>
     <t>02177-588-31</t>
+  </si>
+  <si>
+    <t>MEDU703575 /8</t>
+  </si>
+  <si>
+    <t>MSMU601249 /5</t>
+  </si>
+  <si>
+    <t>MSMU662915 /2</t>
+  </si>
+  <si>
+    <t>00045-506-46</t>
+  </si>
+  <si>
+    <t>00508-515-31</t>
+  </si>
+  <si>
+    <t>ARKU241132 /0</t>
+  </si>
+  <si>
+    <t>TRHU307416 /1</t>
+  </si>
+  <si>
+    <t>00406-506-31</t>
+  </si>
+  <si>
+    <t>00043-511-31</t>
+  </si>
+  <si>
+    <t>00268-511-31</t>
+  </si>
+  <si>
+    <t>,</t>
   </si>
 </sst>
 </file>
@@ -1514,7 +1546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1731,7 +1763,13 @@
     <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1755,14 +1793,29 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3532,10 +3585,21 @@
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
+      <c r="A20" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B20" s="3">
+        <f>'27-10'!H1</f>
+        <v>3</v>
+      </c>
+      <c r="C20" s="3">
+        <f>'27-10'!H2</f>
+        <v>10</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" ref="D20" si="6">B20+C20</f>
+        <v>13</v>
+      </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3565,15 +3629,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D23)</f>
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3633,16 +3697,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4227,16 +4291,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4759,16 +4823,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5495,16 +5559,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6081,16 +6145,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6724,16 +6788,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7250,16 +7314,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7301,7 +7365,7 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="76" t="s">
         <v>309</v>
       </c>
       <c r="C8" s="19">
@@ -7322,7 +7386,7 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="82"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="19">
         <v>21102026</v>
       </c>
@@ -7341,7 +7405,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="82"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="19">
         <v>21102026</v>
       </c>
@@ -7360,7 +7424,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="19">
         <v>21102026</v>
       </c>
@@ -7379,7 +7443,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="84" t="s">
         <v>310</v>
       </c>
       <c r="C12" s="19">
@@ -7400,7 +7464,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="83"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="19">
         <v>21102026</v>
       </c>
@@ -7419,7 +7483,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="83"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="19">
         <v>21102026</v>
       </c>
@@ -7438,7 +7502,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="83"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="19">
         <v>21102026</v>
       </c>
@@ -7457,7 +7521,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="83"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="19">
         <v>21102026</v>
       </c>
@@ -7476,7 +7540,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="83"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="19">
         <v>21102026</v>
       </c>
@@ -7932,16 +7996,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8505,16 +8569,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9137,16 +9201,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9188,7 +9252,7 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="76" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="19">
@@ -9209,7 +9273,7 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="82"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="19">
         <v>26102026</v>
       </c>
@@ -9228,7 +9292,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="82"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="19">
         <v>26102026</v>
       </c>
@@ -9247,7 +9311,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="19">
         <v>26102026</v>
       </c>
@@ -9266,7 +9330,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="82"/>
+      <c r="B12" s="76"/>
       <c r="C12" s="19">
         <v>26102026</v>
       </c>
@@ -9285,7 +9349,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="82"/>
+      <c r="B13" s="76"/>
       <c r="C13" s="19">
         <v>26102026</v>
       </c>
@@ -9418,7 +9482,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>327</v>
+        <v>13</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>14</v>
@@ -9731,16 +9795,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10243,7 +10307,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48D2CC8-9E86-4801-8F04-CBE9B8C2AB40}">
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
@@ -10261,7 +10325,7 @@
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="H1" s="8">
-        <f>COUNTIF(C8:C18,"&lt;&gt;")</f>
+        <f>COUNTIF(C8:C14,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="I1" s="9" t="s">
@@ -10271,35 +10335,35 @@
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="F2" s="8">
-        <f>COUNTIFS(B24:B37,"&lt;&gt;",C24:C37,"VH")</f>
+        <f>COUNTIFS(B19:B35,"&lt;&gt;",C19:C35,"VH")</f>
         <v>0</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8">
-        <f>COUNTA(C24:C31)-F2</f>
-        <v>5</v>
+        <f>COUNTA(C19:C28)-F2</f>
+        <v>10</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="10">
-        <f>COUNTIF(E24:E37,"VIDE")</f>
+        <f>COUNTIF(E19:E35,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10341,7 +10405,7 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="76" t="s">
         <v>359</v>
       </c>
       <c r="C8" s="19">
@@ -10362,7 +10426,7 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="82"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="19">
         <v>27102026</v>
       </c>
@@ -10381,7 +10445,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="82"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="19">
         <v>27102026</v>
       </c>
@@ -10440,357 +10504,418 @@
       <c r="F14" s="67"/>
       <c r="G14" s="20"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="28">
-        <v>8</v>
-      </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="20"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
-        <v>9</v>
-      </c>
-      <c r="B16" s="72"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
+      <c r="A16" s="6"/>
+      <c r="B16" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="K17" s="21" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
-        <v>11</v>
-      </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="20"/>
-    </row>
-    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="15" t="s">
+      <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C18" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D18" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E18" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F18" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>1</v>
+      </c>
+      <c r="B19" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" s="24">
+        <v>3677</v>
+      </c>
+      <c r="F19" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28">
+        <v>2</v>
+      </c>
+      <c r="B20" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="E20" s="28">
+        <v>3678</v>
+      </c>
+      <c r="F20" s="28">
+        <v>20</v>
+      </c>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28">
+        <v>3</v>
+      </c>
+      <c r="B21" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="33"/>
+      <c r="O21"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="28">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="D22" s="66" t="s">
+        <v>289</v>
+      </c>
+      <c r="E22" s="31">
+        <v>3597</v>
+      </c>
+      <c r="F22" s="24">
+        <v>40</v>
+      </c>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="28">
+        <v>5</v>
+      </c>
+      <c r="B23" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="D23" s="67" t="s">
+        <v>295</v>
+      </c>
+      <c r="E23" s="31">
+        <v>3598</v>
+      </c>
+      <c r="F23" s="24">
+        <v>40</v>
+      </c>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B24" s="19">
         <v>27102026</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>350</v>
-      </c>
-      <c r="E24" s="24">
-        <v>3677</v>
-      </c>
-      <c r="F24" s="28">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="D24" s="67" t="s">
+        <v>368</v>
+      </c>
+      <c r="E24" s="31">
+        <v>2745</v>
+      </c>
+      <c r="F24" s="24">
+        <v>40</v>
+      </c>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B25" s="19">
         <v>27102026</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="E25" s="28">
-        <v>3678</v>
-      </c>
-      <c r="F25" s="28">
-        <v>20</v>
-      </c>
-      <c r="H25" s="33"/>
+        <v>371</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>369</v>
+      </c>
+      <c r="E25" s="31">
+        <v>2747</v>
+      </c>
+      <c r="F25" s="24">
+        <v>40</v>
+      </c>
       <c r="I25" s="33"/>
       <c r="J25" s="33"/>
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
-    </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M25" s="33"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B26" s="19">
         <v>27102026</v>
       </c>
-      <c r="C26" s="29" t="s">
-        <v>80</v>
+      <c r="C26" s="35" t="s">
+        <v>375</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-    </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="E26" s="26">
+        <v>2748</v>
+      </c>
+      <c r="F26" s="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B27" s="19">
         <v>27102026</v>
       </c>
-      <c r="C27" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="D27" s="66" t="s">
-        <v>289</v>
-      </c>
-      <c r="E27" s="31">
-        <v>3597</v>
+      <c r="C27" s="35" t="s">
+        <v>377</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="E27" s="25">
+        <v>3652</v>
       </c>
       <c r="F27" s="24">
-        <v>40</v>
-      </c>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-    </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B28" s="19">
         <v>27102026</v>
       </c>
-      <c r="C28" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="D28" s="67" t="s">
-        <v>295</v>
-      </c>
-      <c r="E28" s="31">
-        <v>3598</v>
+      <c r="C28" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="E28" s="25">
+        <v>3653</v>
       </c>
       <c r="F28" s="24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="86"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="91"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="86"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="91"/>
+    </row>
+    <row r="31" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28">
+        <v>1</v>
+      </c>
+      <c r="B34" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C34" s="74" t="s">
+        <v>360</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>361</v>
+      </c>
+      <c r="E34" s="31">
+        <v>3595</v>
+      </c>
+      <c r="F34" s="24">
         <v>40</v>
       </c>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-    </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
-        <v>8</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="24"/>
-    </row>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
-        <v>9</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="24"/>
-    </row>
-    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28">
-        <v>10</v>
-      </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="24"/>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="49"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>15</v>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28">
+        <v>2</v>
+      </c>
+      <c r="B35" s="19">
+        <v>27102026</v>
+      </c>
+      <c r="C35" s="74" t="s">
+        <v>362</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>363</v>
+      </c>
+      <c r="E35" s="31">
+        <v>3596</v>
+      </c>
+      <c r="F35" s="24">
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B36" s="19">
         <v>27102026</v>
       </c>
-      <c r="C36" s="84" t="s">
-        <v>360</v>
+      <c r="C36" s="74" t="s">
+        <v>364</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E36" s="31">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="F36" s="24">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
-        <v>2</v>
-      </c>
-      <c r="B37" s="19">
-        <v>27102026</v>
-      </c>
-      <c r="C37" s="84" t="s">
-        <v>362</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>363</v>
-      </c>
-      <c r="E37" s="31">
-        <v>3596</v>
-      </c>
-      <c r="F37" s="24">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="24"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
-        <v>3</v>
-      </c>
-      <c r="B38" s="19">
-        <v>27102026</v>
-      </c>
-      <c r="C38" s="84" t="s">
-        <v>364</v>
-      </c>
-      <c r="D38" s="43" t="s">
-        <v>365</v>
-      </c>
-      <c r="E38" s="31">
-        <v>3594</v>
-      </c>
-      <c r="F38" s="24">
-        <v>40</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="24"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="24"/>
@@ -10798,28 +10923,8 @@
       <c r="E39" s="31"/>
       <c r="F39" s="24"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="28">
-        <v>5</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="24"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="28">
-        <v>6</v>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="24"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E45" s="21" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E43" s="21" t="s">
         <v>247</v>
       </c>
     </row>
@@ -10829,7 +10934,7 @@
     <mergeCell ref="B8:B10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F20 F36:F41 F24:F32" xr:uid="{5918CB6E-FE11-4CC1-8449-E715B81D557B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F34:F39 F19:F30 F8:F15" xr:uid="{5918CB6E-FE11-4CC1-8449-E715B81D557B}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10889,16 +10994,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11473,16 +11578,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -12107,16 +12212,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -12158,7 +12263,7 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="77" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -12179,7 +12284,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="76"/>
+      <c r="B9" s="78"/>
       <c r="C9" s="19">
         <v>6102026</v>
       </c>
@@ -12198,7 +12303,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="76"/>
+      <c r="B10" s="78"/>
       <c r="C10" s="19">
         <v>6102026</v>
       </c>
@@ -12217,7 +12322,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="76"/>
+      <c r="B11" s="78"/>
       <c r="C11" s="19">
         <v>6102026</v>
       </c>
@@ -12236,7 +12341,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="76"/>
+      <c r="B12" s="78"/>
       <c r="C12" s="57"/>
       <c r="D12" s="51" t="s">
         <v>125</v>
@@ -12253,7 +12358,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="76"/>
+      <c r="B13" s="78"/>
       <c r="C13" s="57"/>
       <c r="D13" s="51" t="s">
         <v>123</v>
@@ -12270,7 +12375,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="76"/>
+      <c r="B14" s="78"/>
       <c r="C14" s="57"/>
       <c r="D14" s="51" t="s">
         <v>121</v>
@@ -12287,7 +12392,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="76"/>
+      <c r="B15" s="78"/>
       <c r="C15" s="19">
         <v>6102026</v>
       </c>
@@ -12306,7 +12411,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="76"/>
+      <c r="B16" s="78"/>
       <c r="C16" s="57"/>
       <c r="D16" s="56" t="s">
         <v>117</v>
@@ -12323,7 +12428,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="76"/>
+      <c r="B17" s="78"/>
       <c r="C17" s="19">
         <v>6102026</v>
       </c>
@@ -12342,7 +12447,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="76"/>
+      <c r="B18" s="78"/>
       <c r="C18" s="57"/>
       <c r="D18" s="51" t="s">
         <v>113</v>
@@ -12359,7 +12464,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="76"/>
+      <c r="B19" s="78"/>
       <c r="C19" s="19">
         <v>6102026</v>
       </c>
@@ -12378,7 +12483,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="76"/>
+      <c r="B20" s="78"/>
       <c r="C20" s="57"/>
       <c r="D20" s="51" t="s">
         <v>109</v>
@@ -12395,7 +12500,7 @@
       <c r="A21" s="17">
         <v>14</v>
       </c>
-      <c r="B21" s="76"/>
+      <c r="B21" s="78"/>
       <c r="C21" s="57"/>
       <c r="D21" s="51" t="s">
         <v>107</v>
@@ -12412,7 +12517,7 @@
       <c r="A22" s="17">
         <v>15</v>
       </c>
-      <c r="B22" s="76"/>
+      <c r="B22" s="78"/>
       <c r="C22" s="57"/>
       <c r="D22" s="51" t="s">
         <v>105</v>
@@ -12429,7 +12534,7 @@
       <c r="A23" s="17">
         <v>16</v>
       </c>
-      <c r="B23" s="76"/>
+      <c r="B23" s="78"/>
       <c r="C23" s="57"/>
       <c r="D23" s="56" t="s">
         <v>103</v>
@@ -12446,7 +12551,7 @@
       <c r="A24" s="17">
         <v>17</v>
       </c>
-      <c r="B24" s="76"/>
+      <c r="B24" s="78"/>
       <c r="C24" s="19">
         <v>6102026</v>
       </c>
@@ -12465,7 +12570,7 @@
       <c r="A25" s="17">
         <v>18</v>
       </c>
-      <c r="B25" s="76"/>
+      <c r="B25" s="78"/>
       <c r="C25" s="19">
         <v>6102026</v>
       </c>
@@ -12484,7 +12589,7 @@
       <c r="A26" s="17">
         <v>19</v>
       </c>
-      <c r="B26" s="76"/>
+      <c r="B26" s="78"/>
       <c r="C26" s="19">
         <v>6102026</v>
       </c>
@@ -12503,7 +12608,7 @@
       <c r="A27" s="17">
         <v>20</v>
       </c>
-      <c r="B27" s="76"/>
+      <c r="B27" s="78"/>
       <c r="C27" s="19">
         <v>6102026</v>
       </c>
@@ -12522,7 +12627,7 @@
       <c r="A28" s="17">
         <v>21</v>
       </c>
-      <c r="B28" s="76"/>
+      <c r="B28" s="78"/>
       <c r="C28" s="57"/>
       <c r="D28" s="56" t="s">
         <v>93</v>
@@ -12539,7 +12644,7 @@
       <c r="A29" s="17">
         <v>22</v>
       </c>
-      <c r="B29" s="76"/>
+      <c r="B29" s="78"/>
       <c r="C29" s="19">
         <v>6102026</v>
       </c>
@@ -12558,7 +12663,7 @@
       <c r="A30" s="17">
         <v>23</v>
       </c>
-      <c r="B30" s="76"/>
+      <c r="B30" s="78"/>
       <c r="C30" s="19">
         <v>6102026</v>
       </c>
@@ -12577,7 +12682,7 @@
       <c r="A31" s="17">
         <v>24</v>
       </c>
-      <c r="B31" s="77"/>
+      <c r="B31" s="79"/>
       <c r="C31" s="19">
         <v>6102026</v>
       </c>
@@ -12814,16 +12919,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -12865,7 +12970,7 @@
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="80" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="19">
@@ -12886,7 +12991,7 @@
       <c r="A9" s="28">
         <v>2</v>
       </c>
-      <c r="B9" s="78"/>
+      <c r="B9" s="80"/>
       <c r="C9" s="19">
         <v>7102026</v>
       </c>
@@ -12905,7 +13010,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="78"/>
+      <c r="B10" s="80"/>
       <c r="C10" s="19">
         <v>7102026</v>
       </c>
@@ -12924,7 +13029,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="78"/>
+      <c r="B11" s="80"/>
       <c r="C11" s="19">
         <v>7102026</v>
       </c>
@@ -12943,7 +13048,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="78"/>
+      <c r="B12" s="80"/>
       <c r="C12" s="19">
         <v>7102026</v>
       </c>
@@ -12962,7 +13067,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="78"/>
+      <c r="B13" s="80"/>
       <c r="C13" s="19">
         <v>7102026</v>
       </c>
@@ -12981,7 +13086,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="78"/>
+      <c r="B14" s="80"/>
       <c r="C14" s="19">
         <v>7102026</v>
       </c>
@@ -13000,7 +13105,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="78"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="19">
         <v>7102026</v>
       </c>
@@ -13019,7 +13124,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="78"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="19">
         <v>7102026</v>
       </c>
@@ -13038,7 +13143,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="78"/>
+      <c r="B17" s="80"/>
       <c r="C17" s="19">
         <v>7102026</v>
       </c>
@@ -13057,7 +13162,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="80" t="s">
         <v>137</v>
       </c>
       <c r="C18" s="19">
@@ -13078,7 +13183,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="78"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="19">
         <v>7102026</v>
       </c>
@@ -13390,16 +13495,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -13920,16 +14025,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -14013,7 +14118,7 @@
       <c r="A10" s="28">
         <v>3</v>
       </c>
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="81" t="s">
         <v>187</v>
       </c>
       <c r="C10" s="19">
@@ -14034,7 +14139,7 @@
       <c r="A11" s="28">
         <v>4</v>
       </c>
-      <c r="B11" s="80"/>
+      <c r="B11" s="82"/>
       <c r="C11" s="19">
         <v>11102026</v>
       </c>
@@ -14053,7 +14158,7 @@
       <c r="A12" s="28">
         <v>5</v>
       </c>
-      <c r="B12" s="80"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="19">
         <v>11102026</v>
       </c>
@@ -14072,7 +14177,7 @@
       <c r="A13" s="28">
         <v>6</v>
       </c>
-      <c r="B13" s="80"/>
+      <c r="B13" s="82"/>
       <c r="C13" s="19">
         <v>11102026</v>
       </c>
@@ -14091,7 +14196,7 @@
       <c r="A14" s="28">
         <v>7</v>
       </c>
-      <c r="B14" s="80"/>
+      <c r="B14" s="82"/>
       <c r="C14" s="19">
         <v>11102026</v>
       </c>
@@ -14110,7 +14215,7 @@
       <c r="A15" s="28">
         <v>8</v>
       </c>
-      <c r="B15" s="81"/>
+      <c r="B15" s="83"/>
       <c r="C15" s="19">
         <v>11102026</v>
       </c>
@@ -14129,7 +14234,7 @@
       <c r="A16" s="28">
         <v>9</v>
       </c>
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="81" t="s">
         <v>188</v>
       </c>
       <c r="C16" s="19">
@@ -14150,7 +14255,7 @@
       <c r="A17" s="28">
         <v>10</v>
       </c>
-      <c r="B17" s="80"/>
+      <c r="B17" s="82"/>
       <c r="C17" s="19">
         <v>11102026</v>
       </c>
@@ -14169,7 +14274,7 @@
       <c r="A18" s="28">
         <v>11</v>
       </c>
-      <c r="B18" s="80"/>
+      <c r="B18" s="82"/>
       <c r="C18" s="19">
         <v>11102026</v>
       </c>
@@ -14188,7 +14293,7 @@
       <c r="A19" s="28">
         <v>12</v>
       </c>
-      <c r="B19" s="80"/>
+      <c r="B19" s="82"/>
       <c r="C19" s="19">
         <v>11102026</v>
       </c>
@@ -14207,7 +14312,7 @@
       <c r="A20" s="28">
         <v>13</v>
       </c>
-      <c r="B20" s="80"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="19">
         <v>11102026</v>
       </c>
@@ -14226,7 +14331,7 @@
       <c r="A21" s="28">
         <v>14</v>
       </c>
-      <c r="B21" s="81"/>
+      <c r="B21" s="83"/>
       <c r="C21" s="19">
         <v>11102026</v>
       </c>
@@ -14657,16 +14762,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
